--- a/xlsx/单位数据.xlsx
+++ b/xlsx/单位数据.xlsx
@@ -76,85 +76,86 @@
     <col min="16" max="16" width="17.5625" customWidth="true"/>
     <col min="17" max="17" width="23.8046875" customWidth="true"/>
     <col min="18" max="18" width="10.9609375" customWidth="true"/>
-    <col min="19" max="19" width="26.453125" customWidth="true"/>
-    <col min="20" max="20" width="8.8828125" customWidth="true"/>
-    <col min="21" max="21" width="9.33984375" customWidth="true"/>
-    <col min="22" max="22" width="10.15234375" customWidth="true"/>
-    <col min="23" max="23" width="11.12890625" customWidth="true"/>
-    <col min="24" max="24" width="66.578125" customWidth="true"/>
-    <col min="25" max="25" width="63.3515625" customWidth="true"/>
-    <col min="26" max="26" width="15.7421875" customWidth="true"/>
-    <col min="27" max="27" width="17.99609375" customWidth="true"/>
-    <col min="28" max="28" width="15.9609375" customWidth="true"/>
-    <col min="29" max="29" width="13.1328125" customWidth="true"/>
-    <col min="30" max="30" width="12.70703125" customWidth="true"/>
-    <col min="31" max="31" width="13.484375" customWidth="true"/>
-    <col min="32" max="32" width="11.11328125" customWidth="true"/>
-    <col min="33" max="33" width="9.31640625" customWidth="true"/>
-    <col min="34" max="34" width="13.6328125" customWidth="true"/>
-    <col min="35" max="35" width="9.33984375" customWidth="true"/>
+    <col min="19" max="19" width="25.01953125" customWidth="true"/>
+    <col min="20" max="20" width="19.85546875" customWidth="true"/>
+    <col min="21" max="21" width="8.8828125" customWidth="true"/>
+    <col min="22" max="22" width="9.33984375" customWidth="true"/>
+    <col min="23" max="23" width="10.15234375" customWidth="true"/>
+    <col min="24" max="24" width="11.12890625" customWidth="true"/>
+    <col min="25" max="25" width="66.578125" customWidth="true"/>
+    <col min="26" max="26" width="63.3515625" customWidth="true"/>
+    <col min="27" max="27" width="15.7421875" customWidth="true"/>
+    <col min="28" max="28" width="17.99609375" customWidth="true"/>
+    <col min="29" max="29" width="15.9609375" customWidth="true"/>
+    <col min="30" max="30" width="13.1328125" customWidth="true"/>
+    <col min="31" max="31" width="12.70703125" customWidth="true"/>
+    <col min="32" max="32" width="13.484375" customWidth="true"/>
+    <col min="33" max="33" width="11.11328125" customWidth="true"/>
+    <col min="34" max="34" width="9.31640625" customWidth="true"/>
+    <col min="35" max="35" width="13.6328125" customWidth="true"/>
     <col min="36" max="36" width="9.33984375" customWidth="true"/>
     <col min="37" max="37" width="9.33984375" customWidth="true"/>
-    <col min="38" max="38" width="15.02734375" customWidth="true"/>
+    <col min="38" max="38" width="9.33984375" customWidth="true"/>
     <col min="39" max="39" width="15.02734375" customWidth="true"/>
     <col min="40" max="40" width="15.02734375" customWidth="true"/>
-    <col min="41" max="41" width="11.60546875" customWidth="true"/>
+    <col min="41" max="41" width="15.02734375" customWidth="true"/>
     <col min="42" max="42" width="11.60546875" customWidth="true"/>
     <col min="43" max="43" width="11.60546875" customWidth="true"/>
-    <col min="44" max="44" width="35.6640625" customWidth="true"/>
-    <col min="45" max="45" width="15.3984375" customWidth="true"/>
-    <col min="46" max="46" width="19.21484375" customWidth="true"/>
-    <col min="47" max="47" width="21.359375" customWidth="true"/>
+    <col min="44" max="44" width="11.60546875" customWidth="true"/>
+    <col min="45" max="45" width="35.6640625" customWidth="true"/>
+    <col min="46" max="46" width="15.3984375" customWidth="true"/>
+    <col min="47" max="47" width="19.21484375" customWidth="true"/>
     <col min="48" max="48" width="21.359375" customWidth="true"/>
-    <col min="49" max="49" width="16.3359375" customWidth="true"/>
-    <col min="50" max="50" width="16.44140625" customWidth="true"/>
-    <col min="51" max="51" width="14.16796875" customWidth="true"/>
-    <col min="52" max="52" width="19.203125" customWidth="true"/>
-    <col min="53" max="53" width="15.73046875" customWidth="true"/>
-    <col min="54" max="54" width="14.5625" customWidth="true"/>
-    <col min="55" max="55" width="17.04296875" customWidth="true"/>
-    <col min="56" max="56" width="19.3828125" customWidth="true"/>
-    <col min="57" max="57" width="13.5859375" customWidth="true"/>
-    <col min="58" max="58" width="26.04296875" customWidth="true"/>
-    <col min="59" max="59" width="19.53125" customWidth="true"/>
-    <col min="60" max="60" width="26.9609375" customWidth="true"/>
-    <col min="61" max="61" width="20.75" customWidth="true"/>
-    <col min="62" max="62" width="25.19140625" customWidth="true"/>
+    <col min="49" max="49" width="21.359375" customWidth="true"/>
+    <col min="50" max="50" width="16.3359375" customWidth="true"/>
+    <col min="51" max="51" width="16.44140625" customWidth="true"/>
+    <col min="52" max="52" width="14.16796875" customWidth="true"/>
+    <col min="53" max="53" width="19.203125" customWidth="true"/>
+    <col min="54" max="54" width="15.73046875" customWidth="true"/>
+    <col min="55" max="55" width="14.5625" customWidth="true"/>
+    <col min="56" max="56" width="17.04296875" customWidth="true"/>
+    <col min="57" max="57" width="19.3828125" customWidth="true"/>
+    <col min="58" max="58" width="13.5859375" customWidth="true"/>
+    <col min="59" max="59" width="26.04296875" customWidth="true"/>
+    <col min="60" max="60" width="19.53125" customWidth="true"/>
+    <col min="61" max="61" width="26.9609375" customWidth="true"/>
+    <col min="62" max="62" width="20.75" customWidth="true"/>
     <col min="63" max="63" width="25.19140625" customWidth="true"/>
-    <col min="64" max="64" width="18.7109375" customWidth="true"/>
-    <col min="65" max="65" width="17.84765625" customWidth="true"/>
-    <col min="66" max="66" width="15.0859375" customWidth="true"/>
-    <col min="67" max="67" width="13.1328125" customWidth="true"/>
-    <col min="68" max="68" width="15.1796875" customWidth="true"/>
-    <col min="69" max="69" width="28.48046875" customWidth="true"/>
-    <col min="70" max="70" width="19.2578125" customWidth="true"/>
-    <col min="71" max="71" width="13.1328125" customWidth="true"/>
-    <col min="72" max="72" width="15.53125" customWidth="true"/>
-    <col min="73" max="73" width="14.74609375" customWidth="true"/>
-    <col min="74" max="74" width="18.7109375" customWidth="true"/>
-    <col min="75" max="75" width="19.53125" customWidth="true"/>
-    <col min="76" max="76" width="15.96875" customWidth="true"/>
-    <col min="77" max="77" width="15.95703125" customWidth="true"/>
-    <col min="78" max="78" width="22.1640625" customWidth="true"/>
-    <col min="79" max="79" width="27.94921875" customWidth="true"/>
-    <col min="80" max="80" width="13.1328125" customWidth="true"/>
-    <col min="81" max="81" width="15.96875" customWidth="true"/>
-    <col min="82" max="82" width="35.6640625" customWidth="true"/>
-    <col min="83" max="83" width="19.515625" customWidth="true"/>
-    <col min="84" max="84" width="14.7734375" customWidth="true"/>
-    <col min="85" max="85" width="28.60546875" customWidth="true"/>
-    <col min="86" max="86" width="18.99609375" customWidth="true"/>
-    <col min="87" max="87" width="19.53515625" customWidth="true"/>
+    <col min="64" max="64" width="25.19140625" customWidth="true"/>
+    <col min="65" max="65" width="18.7109375" customWidth="true"/>
+    <col min="66" max="66" width="17.84765625" customWidth="true"/>
+    <col min="67" max="67" width="15.0859375" customWidth="true"/>
+    <col min="68" max="68" width="13.1328125" customWidth="true"/>
+    <col min="69" max="69" width="15.1796875" customWidth="true"/>
+    <col min="70" max="70" width="28.48046875" customWidth="true"/>
+    <col min="71" max="71" width="19.2578125" customWidth="true"/>
+    <col min="72" max="72" width="13.1328125" customWidth="true"/>
+    <col min="73" max="73" width="15.53125" customWidth="true"/>
+    <col min="74" max="74" width="14.74609375" customWidth="true"/>
+    <col min="75" max="75" width="18.7109375" customWidth="true"/>
+    <col min="76" max="76" width="19.53125" customWidth="true"/>
+    <col min="77" max="77" width="15.96875" customWidth="true"/>
+    <col min="78" max="78" width="15.95703125" customWidth="true"/>
+    <col min="79" max="79" width="22.1640625" customWidth="true"/>
+    <col min="80" max="80" width="27.94921875" customWidth="true"/>
+    <col min="81" max="81" width="13.1328125" customWidth="true"/>
+    <col min="82" max="82" width="15.96875" customWidth="true"/>
+    <col min="83" max="83" width="35.6640625" customWidth="true"/>
+    <col min="84" max="84" width="19.515625" customWidth="true"/>
+    <col min="85" max="85" width="14.7734375" customWidth="true"/>
+    <col min="86" max="86" width="28.60546875" customWidth="true"/>
+    <col min="87" max="87" width="18.99609375" customWidth="true"/>
     <col min="88" max="88" width="19.53515625" customWidth="true"/>
-    <col min="89" max="89" width="18.55859375" customWidth="true"/>
-    <col min="90" max="90" width="36.1015625" customWidth="true"/>
-    <col min="91" max="91" width="13.1328125" customWidth="true"/>
-    <col min="92" max="92" width="11.234375" customWidth="true"/>
-    <col min="93" max="93" width="14.14453125" customWidth="true"/>
-    <col min="94" max="94" width="19.7265625" customWidth="true"/>
-    <col min="95" max="95" width="29.76171875" customWidth="true"/>
-    <col min="96" max="96" width="17.86328125" customWidth="true"/>
-    <col min="97" max="97" width="53.546875" customWidth="true"/>
+    <col min="89" max="89" width="19.53515625" customWidth="true"/>
+    <col min="90" max="90" width="18.55859375" customWidth="true"/>
+    <col min="91" max="91" width="36.1015625" customWidth="true"/>
+    <col min="92" max="92" width="13.1328125" customWidth="true"/>
+    <col min="93" max="93" width="11.234375" customWidth="true"/>
+    <col min="94" max="94" width="14.14453125" customWidth="true"/>
+    <col min="95" max="95" width="19.7265625" customWidth="true"/>
+    <col min="96" max="96" width="29.76171875" customWidth="true"/>
+    <col min="97" max="97" width="17.86328125" customWidth="true"/>
+    <col min="98" max="98" width="53.546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -255,390 +256,395 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>英雄技能</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>基础速度</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>占用人口</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>修理时间</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>目标允许</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>投射物图像</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>攻击类型</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>要求动画名</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>种族</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>魔法初始数量</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>魔法最大值</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>装甲类型</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>缩放</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>主属性</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>初始力量</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>初始敏捷</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>初始智力</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>每等级提升力量</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>每等级提升敏捷</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>每等级提升智力</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>颜色值(红)</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>颜色值(绿)</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>颜色值(蓝)</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>提示工具 -唤醒</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>视野范围(夜晚)</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>模型缩放</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>按钮位置 - 普通 (X)</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>按钮位置 - 普通 (Y)</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>最大库存量</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>建筑地面纹理</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>修理金子消耗</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>购买时间间隔</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>武器类型</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>售出单位</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>购买开始时间</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>编辑器后缀</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>动画伤害点</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>阴影图像(建筑)</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>攻击 2 - 投射物图像</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>攻击武器声音</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>射弹弧度</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>射弹速率</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>攻击 2 - 射弹速率</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>攻击 2 - 攻击类型</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>生命回复类型</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>动画回复点</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>伤害骰子数量</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>转身速度</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>使用科技</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>魔法回复</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>默认主动技能</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>穿透伤害距离</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>攻击范围</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>攻击 2 - 攻击范围</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>图标 - 计分屏</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>动画 - 行走速度</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>允许攻击模式</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>称谓</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>射弹自导允许</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>主动攻击范围</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>动画 - 跑步速度</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>提示工具 -重生</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>称谓数量</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>生命回复</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>单位声音设置</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>需求 - 等级 3</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>需求 - 等级 2</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>修理木材消耗</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>要求动画名 - 附加动画</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>伤害骰子面数</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>攻击间隔2</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>碰撞体积</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>穿透伤害范围</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>木材奖励 - 基础值</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>动画 - 魔法施放点</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>编辑器附加数据</t>
         </is>
@@ -742,390 +748,395 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>heroAbilList</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>level</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>spd</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>fused</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>reptm</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>targs1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Missileart_1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>atkType1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>animProps</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>mana0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>manaN</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>movetp</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>armor</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>scale</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>STRplus</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>AGIplus</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>INTplus</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Awakentip</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>nsight</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>modelScale</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>Buttonpos_1</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Buttonpos_2</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>stockMax</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>uberSplat</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>goldRep</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>stockRegen</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>weapTp1</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>Sellunits</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>stockStart</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>EditorSuffix</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>dmgpt1</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>buildingShadow</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>Missileart_2</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>weapType1</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>Missilearc_1</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>Missilespeed_1</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>Missilespeed_2</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>atkType2</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>regenType</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>backSw1</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>dice1</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>turnRate</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>upgrades</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>regenMana</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>spillDist1</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>rangeN1</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>rangeN2</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>ScoreScreenIcon</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>weapsOn</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>Propernames</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>MissileHoming_1</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>acquire</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>Revivetip</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>nameCount</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>regenHP</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>unitSound</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>Requires2</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>Requires1</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>lumberRep</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>Attachmentanimprops</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>sides1</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>cool2</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>collision</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>spillRadius1</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>lumberbountyplus</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>castpt</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>W2LObject</t>
         </is>
@@ -1172,22 +1183,22 @@
           <t>Aneu,Avul,Apit</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>Ecen</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>"XC":"商店NPC.xlsx  【商店npc.uobj】  "</t>
         </is>
@@ -1228,51 +1239,51 @@
           <t>Ault,AInv</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>5.0</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>100.0</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>4.0</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>1.0</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BA4" t="n">
         <v>3600.0</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BD4" t="n">
         <v>180.0</v>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>Rema</t>
         </is>
       </c>
-      <c r="CF4" t="n">
+      <c r="CG4" t="n">
         <v>4.0</v>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>TWN3,TALT</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
+      <c r="CR4" t="n">
         <v>2000.0</v>
       </c>
-      <c r="CS4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1297,49 +1308,49 @@
           <t>Adtg,AInv,Ault</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>40.0</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>100.0</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BJ5" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BK5" t="n">
         <v>1100.0</v>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>Reib</t>
         </is>
-      </c>
-      <c r="BU5" t="n">
-        <v>1000.0</v>
       </c>
       <c r="BV5" t="n">
         <v>1000.0</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="BW5" t="n">
         <v>1000.0</v>
       </c>
-      <c r="CF5" t="n">
+      <c r="CC5" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CG5" t="n">
         <v>10.0</v>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CN5" t="n">
+      <c r="CO5" t="n">
         <v>2.25</v>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1364,34 +1375,34 @@
           <t>A0DB,AInv,Ault</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>40.0</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>100.0</v>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="CF6" t="n">
+      <c r="CG6" t="n">
         <v>10.0</v>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CO6" t="n">
+      <c r="CP6" t="n">
         <v>30.0</v>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1419,35 +1430,35 @@
           <t>A044,AInv,Ault</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>360.0</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>5.0</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>100.0</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>2.0</v>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>（玛维）</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="BR7" t="n">
+      <c r="BS7" t="n">
         <v>0.5</v>
       </c>
-      <c r="CF7" t="n">
+      <c r="CG7" t="n">
         <v>5.0</v>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1511,145 +1522,145 @@
           <t>A09V,AInv</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>320.0</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>5.0</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>ground,ward,structure,debris,item</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>.mdl</t>
         </is>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>700.0</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>100.0</v>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>16.0</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>3.0</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>1.7</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>2.0</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>1.2</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>1.0</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>1500.0</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>Abilities\Weapons\WaterElementalMissile\WaterElementalMissile.mdl</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>MetalHeavySlice</t>
         </is>
-      </c>
-      <c r="BI8" t="n">
-        <v>0.0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.0</v>
       </c>
       <c r="BK8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL8" t="n">
         <v>2000.0</v>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>spells</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>Rnam,Rnat,Rguv</t>
         </is>
       </c>
-      <c r="BU8" t="n">
+      <c r="BV8" t="n">
         <v>200.0</v>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNSeaWitch.blp</t>
         </is>
       </c>
-      <c r="BY8" t="n">
+      <c r="BZ8" t="n">
         <v>3.0</v>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>索菲</t>
         </is>
       </c>
-      <c r="CB8" t="n">
+      <c r="CC8" t="n">
         <v>800.0</v>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="CF8" t="n">
+      <c r="CG8" t="n">
         <v>2.0</v>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>NagaSiren</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CK8" t="n">
+      <c r="CL8" t="n">
         <v>500.0</v>
       </c>
-      <c r="CN8" t="n">
+      <c r="CO8" t="n">
         <v>2.0</v>
       </c>
-      <c r="CO8" t="n">
+      <c r="CP8" t="n">
         <v>30.0</v>
       </c>
-      <c r="CS8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1677,59 +1688,59 @@
       <c r="I9" t="n">
         <v>1.0</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>30.0</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>350.0</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>5.0</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>100.0</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>horse</t>
         </is>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>3.0</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>500.0</v>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="BR9" t="n">
+      <c r="BS9" t="n">
         <v>1.0</v>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>黑暗骑士</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="CF9" t="n">
+      <c r="CG9" t="n">
         <v>1.0</v>
       </c>
-      <c r="CM9" t="n">
+      <c r="CN9" t="n">
         <v>10.0</v>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1790,180 +1801,180 @@
           <t>A09X,A09P</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>50.0</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>300.0</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>5.0</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>ground,ward,structure,tree,debris,item,air</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Abilities\Weapons\Rifle\RifleImpact.mdl</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>300.0</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>400.0</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.0</v>
       </c>
       <c r="AK10" t="n">
         <v>1.0</v>
       </c>
       <c r="AL10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM10" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.0</v>
       </c>
       <c r="AN10" t="n">
         <v>0.0</v>
       </c>
       <c r="AO10" t="n">
-        <v>155.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP10" t="n">
         <v>155.0</v>
       </c>
       <c r="AQ10" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="AR10" t="n">
         <v>55.0</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>1000.0</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.0</v>
       </c>
       <c r="AV10" t="n">
         <v>2.0</v>
       </c>
       <c r="AW10" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AX10" t="n">
         <v>1.0</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>mline</t>
         </is>
       </c>
-      <c r="BC10" t="n">
+      <c r="BD10" t="n">
         <v>180.0</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BF10" t="n">
         <v>0.17</v>
       </c>
-      <c r="BH10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BK10" t="n">
         <v>10000.0</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BO10" t="n">
         <v>0.7</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BP10" t="n">
         <v>1.0</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BQ10" t="n">
         <v>0.3</v>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="BR10" t="n">
+      <c r="BS10" t="n">
         <v>0.0</v>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>A0AM</t>
         </is>
       </c>
-      <c r="BT10" t="n">
+      <c r="BU10" t="n">
         <v>150.0</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="BV10" t="n">
         <v>600.0</v>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNMarine.blp</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>掉队士兵</t>
         </is>
       </c>
-      <c r="CA10" t="n">
+      <c r="CB10" t="n">
         <v>1.0</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CC10" t="n">
         <v>1000.0</v>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>Uther</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>mechanical</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>TWN3,TALT</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="CM10" t="n">
+      <c r="CN10" t="n">
         <v>1.0</v>
       </c>
-      <c r="CP10" t="n">
+      <c r="CQ10" t="n">
         <v>50.0</v>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2014,71 +2025,71 @@
           <t>Apg2,AInv</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>300.0</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>40.0</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>alternate</t>
         </is>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>200.0</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>21.0</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>10.0</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>24.0</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>3.0</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>复活宙斯(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>1.5</v>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNAvatar.blp</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>宙斯</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>复活宙斯(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>Muradin</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2112,31 +2123,31 @@
       <c r="I12" t="n">
         <v>4.0</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>300.0</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>40.0</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>80.0</v>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>Rhan,Rhla</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CS12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2166,75 +2177,80 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>A01B,A09V,AInv</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V13" t="n">
         <v>320.0</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>5.0</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>pierce</t>
         </is>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>500.0</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>100.0</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>1.0</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>1500.0</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BJ13" t="n">
         <v>0.0</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BK13" t="n">
         <v>2000.0</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BP13" t="n">
         <v>3.0</v>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BR13" t="inlineStr">
         <is>
           <t>Rguv,R001</t>
         </is>
       </c>
-      <c r="BU13" t="n">
+      <c r="BV13" t="n">
         <v>900.0</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="BW13" t="n">
         <v>1000.0</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CC13" t="n">
         <v>1000.0</v>
       </c>
-      <c r="CF13" t="n">
+      <c r="CG13" t="n">
         <v>1.0</v>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CK13" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CK13" t="n">
+      <c r="CL13" t="n">
         <v>500.0</v>
       </c>
-      <c r="CO13" t="n">
+      <c r="CP13" t="n">
         <v>30.0</v>
       </c>
-      <c r="CS13" t="inlineStr">
+      <c r="CT13" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2290,129 +2306,129 @@
           <t>AInv,A0PD</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>50.0</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>320.0</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>40.0</v>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>90.0</v>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>Flesh</t>
         </is>
       </c>
-      <c r="AG14" t="n">
+      <c r="AH14" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
         <v>19.0</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AK14" t="n">
         <v>24.0</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AL14" t="n">
         <v>16.0</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AM14" t="n">
         <v>2.25</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AN14" t="n">
         <v>1.75</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AO14" t="n">
         <v>1.7</v>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="BC14" t="n">
+      <c r="BD14" t="n">
         <v>180.0</v>
       </c>
-      <c r="BD14" t="inlineStr">
+      <c r="BE14" t="inlineStr">
         <is>
           <t>(剑魔附身)</t>
         </is>
       </c>
-      <c r="BM14" t="inlineStr">
+      <c r="BN14" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="BO14" t="n">
+      <c r="BP14" t="n">
         <v>3.0</v>
       </c>
-      <c r="BQ14" t="inlineStr">
+      <c r="BR14" t="inlineStr">
         <is>
           <t>Robs,Roar</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>UI\Glues\ScoreScreen\scorescreen-hero-chaosblademaster.blp</t>
         </is>
       </c>
-      <c r="BX14" t="n">
+      <c r="BY14" t="n">
         <v>290.0</v>
       </c>
-      <c r="BZ14" t="inlineStr">
+      <c r="CA14" t="inlineStr">
         <is>
           <t>服部半藏</t>
         </is>
       </c>
-      <c r="CC14" t="n">
+      <c r="CD14" t="n">
         <v>300.0</v>
       </c>
-      <c r="CD14" t="inlineStr">
+      <c r="CE14" t="inlineStr">
         <is>
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="CE14" t="n">
+      <c r="CF14" t="n">
         <v>1.0</v>
       </c>
-      <c r="CF14" t="n">
+      <c r="CG14" t="n">
         <v>0.25</v>
       </c>
-      <c r="CG14" t="inlineStr">
+      <c r="CH14" t="inlineStr">
         <is>
           <t>HeroBladeMaster</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="CL14" t="inlineStr">
+      <c r="CM14" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CM14" t="n">
+      <c r="CN14" t="n">
         <v>10.0</v>
       </c>
-      <c r="CR14" t="n">
+      <c r="CS14" t="n">
         <v>0.3</v>
       </c>
-      <c r="CS14" t="inlineStr">
+      <c r="CT14" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>

--- a/xlsx/单位数据.xlsx
+++ b/xlsx/单位数据.xlsx
@@ -64,7 +64,7 @@
     <col min="4" max="4" width="70.3125" customWidth="true"/>
     <col min="5" max="5" width="70.3125" customWidth="true"/>
     <col min="6" max="6" width="16.62109375" customWidth="true"/>
-    <col min="7" max="7" width="7.44140625" customWidth="true"/>
+    <col min="7" max="7" width="11.234375" customWidth="true"/>
     <col min="8" max="8" width="9.33984375" customWidth="true"/>
     <col min="9" max="9" width="13.1328125" customWidth="true"/>
     <col min="10" max="10" width="10.0390625" customWidth="true"/>
@@ -73,89 +73,105 @@
     <col min="13" max="13" width="19.53125" customWidth="true"/>
     <col min="14" max="14" width="19.53125" customWidth="true"/>
     <col min="15" max="15" width="15.4765625" customWidth="true"/>
-    <col min="16" max="16" width="17.5625" customWidth="true"/>
-    <col min="17" max="17" width="23.8046875" customWidth="true"/>
-    <col min="18" max="18" width="10.9609375" customWidth="true"/>
-    <col min="19" max="19" width="25.01953125" customWidth="true"/>
-    <col min="20" max="20" width="19.85546875" customWidth="true"/>
-    <col min="21" max="21" width="8.8828125" customWidth="true"/>
-    <col min="22" max="22" width="9.33984375" customWidth="true"/>
-    <col min="23" max="23" width="10.15234375" customWidth="true"/>
-    <col min="24" max="24" width="11.12890625" customWidth="true"/>
-    <col min="25" max="25" width="66.578125" customWidth="true"/>
-    <col min="26" max="26" width="63.3515625" customWidth="true"/>
-    <col min="27" max="27" width="15.7421875" customWidth="true"/>
-    <col min="28" max="28" width="17.99609375" customWidth="true"/>
-    <col min="29" max="29" width="15.9609375" customWidth="true"/>
-    <col min="30" max="30" width="13.1328125" customWidth="true"/>
-    <col min="31" max="31" width="12.70703125" customWidth="true"/>
-    <col min="32" max="32" width="13.484375" customWidth="true"/>
-    <col min="33" max="33" width="11.11328125" customWidth="true"/>
-    <col min="34" max="34" width="9.31640625" customWidth="true"/>
-    <col min="35" max="35" width="13.6328125" customWidth="true"/>
-    <col min="36" max="36" width="9.33984375" customWidth="true"/>
-    <col min="37" max="37" width="9.33984375" customWidth="true"/>
+    <col min="16" max="16" width="11.5078125" customWidth="true"/>
+    <col min="17" max="17" width="17.5625" customWidth="true"/>
+    <col min="18" max="18" width="23.8046875" customWidth="true"/>
+    <col min="19" max="19" width="10.9609375" customWidth="true"/>
+    <col min="20" max="20" width="40.3671875" customWidth="true"/>
+    <col min="21" max="21" width="42.15234375" customWidth="true"/>
+    <col min="22" max="22" width="8.8828125" customWidth="true"/>
+    <col min="23" max="23" width="10.28515625" customWidth="true"/>
+    <col min="24" max="24" width="10.15234375" customWidth="true"/>
+    <col min="25" max="25" width="11.12890625" customWidth="true"/>
+    <col min="26" max="26" width="52.07421875" customWidth="true"/>
+    <col min="27" max="27" width="66.578125" customWidth="true"/>
+    <col min="28" max="28" width="19.53125" customWidth="true"/>
+    <col min="29" max="29" width="15.7421875" customWidth="true"/>
+    <col min="30" max="30" width="17.99609375" customWidth="true"/>
+    <col min="31" max="31" width="15.9609375" customWidth="true"/>
+    <col min="32" max="32" width="13.1328125" customWidth="true"/>
+    <col min="33" max="33" width="12.70703125" customWidth="true"/>
+    <col min="34" max="34" width="13.484375" customWidth="true"/>
+    <col min="35" max="35" width="11.11328125" customWidth="true"/>
+    <col min="36" max="36" width="9.31640625" customWidth="true"/>
+    <col min="37" max="37" width="13.6328125" customWidth="true"/>
     <col min="38" max="38" width="9.33984375" customWidth="true"/>
-    <col min="39" max="39" width="15.02734375" customWidth="true"/>
-    <col min="40" max="40" width="15.02734375" customWidth="true"/>
+    <col min="39" max="39" width="9.33984375" customWidth="true"/>
+    <col min="40" max="40" width="9.33984375" customWidth="true"/>
     <col min="41" max="41" width="15.02734375" customWidth="true"/>
-    <col min="42" max="42" width="11.60546875" customWidth="true"/>
-    <col min="43" max="43" width="11.60546875" customWidth="true"/>
+    <col min="42" max="42" width="15.02734375" customWidth="true"/>
+    <col min="43" max="43" width="15.02734375" customWidth="true"/>
     <col min="44" max="44" width="11.60546875" customWidth="true"/>
-    <col min="45" max="45" width="35.6640625" customWidth="true"/>
-    <col min="46" max="46" width="15.3984375" customWidth="true"/>
-    <col min="47" max="47" width="19.21484375" customWidth="true"/>
-    <col min="48" max="48" width="21.359375" customWidth="true"/>
-    <col min="49" max="49" width="21.359375" customWidth="true"/>
-    <col min="50" max="50" width="16.3359375" customWidth="true"/>
-    <col min="51" max="51" width="16.44140625" customWidth="true"/>
-    <col min="52" max="52" width="14.16796875" customWidth="true"/>
-    <col min="53" max="53" width="19.203125" customWidth="true"/>
-    <col min="54" max="54" width="15.73046875" customWidth="true"/>
-    <col min="55" max="55" width="14.5625" customWidth="true"/>
-    <col min="56" max="56" width="17.04296875" customWidth="true"/>
-    <col min="57" max="57" width="19.3828125" customWidth="true"/>
-    <col min="58" max="58" width="13.5859375" customWidth="true"/>
-    <col min="59" max="59" width="26.04296875" customWidth="true"/>
-    <col min="60" max="60" width="19.53125" customWidth="true"/>
-    <col min="61" max="61" width="26.9609375" customWidth="true"/>
-    <col min="62" max="62" width="20.75" customWidth="true"/>
-    <col min="63" max="63" width="25.19140625" customWidth="true"/>
-    <col min="64" max="64" width="25.19140625" customWidth="true"/>
-    <col min="65" max="65" width="18.7109375" customWidth="true"/>
-    <col min="66" max="66" width="17.84765625" customWidth="true"/>
-    <col min="67" max="67" width="15.0859375" customWidth="true"/>
-    <col min="68" max="68" width="13.1328125" customWidth="true"/>
-    <col min="69" max="69" width="15.1796875" customWidth="true"/>
-    <col min="70" max="70" width="28.48046875" customWidth="true"/>
-    <col min="71" max="71" width="19.2578125" customWidth="true"/>
-    <col min="72" max="72" width="13.1328125" customWidth="true"/>
-    <col min="73" max="73" width="15.53125" customWidth="true"/>
-    <col min="74" max="74" width="14.74609375" customWidth="true"/>
-    <col min="75" max="75" width="18.7109375" customWidth="true"/>
-    <col min="76" max="76" width="19.53125" customWidth="true"/>
-    <col min="77" max="77" width="15.96875" customWidth="true"/>
-    <col min="78" max="78" width="15.95703125" customWidth="true"/>
-    <col min="79" max="79" width="22.1640625" customWidth="true"/>
-    <col min="80" max="80" width="27.94921875" customWidth="true"/>
-    <col min="81" max="81" width="13.1328125" customWidth="true"/>
-    <col min="82" max="82" width="15.96875" customWidth="true"/>
-    <col min="83" max="83" width="35.6640625" customWidth="true"/>
-    <col min="84" max="84" width="19.515625" customWidth="true"/>
-    <col min="85" max="85" width="14.7734375" customWidth="true"/>
-    <col min="86" max="86" width="28.60546875" customWidth="true"/>
-    <col min="87" max="87" width="18.99609375" customWidth="true"/>
-    <col min="88" max="88" width="19.53515625" customWidth="true"/>
-    <col min="89" max="89" width="19.53515625" customWidth="true"/>
-    <col min="90" max="90" width="18.55859375" customWidth="true"/>
-    <col min="91" max="91" width="36.1015625" customWidth="true"/>
+    <col min="45" max="45" width="11.60546875" customWidth="true"/>
+    <col min="46" max="46" width="11.60546875" customWidth="true"/>
+    <col min="47" max="47" width="20.296875" customWidth="true"/>
+    <col min="48" max="48" width="35.6640625" customWidth="true"/>
+    <col min="49" max="49" width="15.3984375" customWidth="true"/>
+    <col min="50" max="50" width="15.3984375" customWidth="true"/>
+    <col min="51" max="51" width="19.21484375" customWidth="true"/>
+    <col min="52" max="52" width="21.359375" customWidth="true"/>
+    <col min="53" max="53" width="21.359375" customWidth="true"/>
+    <col min="54" max="54" width="16.3359375" customWidth="true"/>
+    <col min="55" max="55" width="16.44140625" customWidth="true"/>
+    <col min="56" max="56" width="14.16796875" customWidth="true"/>
+    <col min="57" max="57" width="19.203125" customWidth="true"/>
+    <col min="58" max="58" width="14.80859375" customWidth="true"/>
+    <col min="59" max="59" width="15.73046875" customWidth="true"/>
+    <col min="60" max="60" width="11.234375" customWidth="true"/>
+    <col min="61" max="61" width="10.7890625" customWidth="true"/>
+    <col min="62" max="62" width="14.5625" customWidth="true"/>
+    <col min="63" max="63" width="17.04296875" customWidth="true"/>
+    <col min="64" max="64" width="19.88671875" customWidth="true"/>
+    <col min="65" max="65" width="19.3828125" customWidth="true"/>
+    <col min="66" max="66" width="13.5859375" customWidth="true"/>
+    <col min="67" max="67" width="34.32421875" customWidth="true"/>
+    <col min="68" max="68" width="19.53125" customWidth="true"/>
+    <col min="69" max="69" width="26.9609375" customWidth="true"/>
+    <col min="70" max="70" width="20.75" customWidth="true"/>
+    <col min="71" max="71" width="25.19140625" customWidth="true"/>
+    <col min="72" max="72" width="25.19140625" customWidth="true"/>
+    <col min="73" max="73" width="18.7109375" customWidth="true"/>
+    <col min="74" max="74" width="17.84765625" customWidth="true"/>
+    <col min="75" max="75" width="15.0859375" customWidth="true"/>
+    <col min="76" max="76" width="14.0703125" customWidth="true"/>
+    <col min="77" max="77" width="13.1328125" customWidth="true"/>
+    <col min="78" max="78" width="18.09375" customWidth="true"/>
+    <col min="79" max="79" width="15.1796875" customWidth="true"/>
+    <col min="80" max="80" width="28.48046875" customWidth="true"/>
+    <col min="81" max="81" width="19.2578125" customWidth="true"/>
+    <col min="82" max="82" width="13.1328125" customWidth="true"/>
+    <col min="83" max="83" width="19.76171875" customWidth="true"/>
+    <col min="84" max="84" width="15.53125" customWidth="true"/>
+    <col min="85" max="85" width="14.74609375" customWidth="true"/>
+    <col min="86" max="86" width="18.7109375" customWidth="true"/>
+    <col min="87" max="87" width="19.53125" customWidth="true"/>
+    <col min="88" max="88" width="15.96875" customWidth="true"/>
+    <col min="89" max="89" width="15.95703125" customWidth="true"/>
+    <col min="90" max="90" width="22.1640625" customWidth="true"/>
+    <col min="91" max="91" width="27.94921875" customWidth="true"/>
     <col min="92" max="92" width="13.1328125" customWidth="true"/>
-    <col min="93" max="93" width="11.234375" customWidth="true"/>
-    <col min="94" max="94" width="14.14453125" customWidth="true"/>
-    <col min="95" max="95" width="19.7265625" customWidth="true"/>
-    <col min="96" max="96" width="29.76171875" customWidth="true"/>
-    <col min="97" max="97" width="17.86328125" customWidth="true"/>
-    <col min="98" max="98" width="53.546875" customWidth="true"/>
+    <col min="93" max="93" width="17.93359375" customWidth="true"/>
+    <col min="94" max="94" width="15.96875" customWidth="true"/>
+    <col min="95" max="95" width="20.1796875" customWidth="true"/>
+    <col min="96" max="96" width="35.6640625" customWidth="true"/>
+    <col min="97" max="97" width="19.515625" customWidth="true"/>
+    <col min="98" max="98" width="14.7734375" customWidth="true"/>
+    <col min="99" max="99" width="28.60546875" customWidth="true"/>
+    <col min="100" max="100" width="19.2109375" customWidth="true"/>
+    <col min="101" max="101" width="19.53515625" customWidth="true"/>
+    <col min="102" max="102" width="19.53515625" customWidth="true"/>
+    <col min="103" max="103" width="18.55859375" customWidth="true"/>
+    <col min="104" max="104" width="36.1015625" customWidth="true"/>
+    <col min="105" max="105" width="13.1328125" customWidth="true"/>
+    <col min="106" max="106" width="11.234375" customWidth="true"/>
+    <col min="107" max="107" width="14.14453125" customWidth="true"/>
+    <col min="108" max="108" width="18.82421875" customWidth="true"/>
+    <col min="109" max="109" width="19.76171875" customWidth="true"/>
+    <col min="110" max="110" width="19.7265625" customWidth="true"/>
+    <col min="111" max="111" width="29.76171875" customWidth="true"/>
+    <col min="112" max="112" width="11.234375" customWidth="true"/>
+    <col min="113" max="113" width="17.86328125" customWidth="true"/>
+    <col min="114" max="114" width="53.546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -236,415 +252,495 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>提供人口</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>需求 -使用等级数</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>训练单位</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>英雄技能</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>基础速度</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>占用人口</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>修理时间</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>路径纹理</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>目标允许</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>投射物图像</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>攻击类型</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>要求动画名</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>种族</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>魔法初始数量</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>魔法最大值</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>装甲类型</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>缩放</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>主属性</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>初始力量</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>初始敏捷</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>初始智力</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>每等级提升力量</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>每等级提升敏捷</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>每等级提升智力</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>颜色值(红)</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>颜色值(绿)</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>颜色值(蓝)</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>高度</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>提示工具 -唤醒</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>视野范围(白天)</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
         <is>
           <t>视野范围(夜晚)</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>模型缩放</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>按钮位置 - 普通 (X)</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>按钮位置 - 普通 (Y)</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>最大库存量</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>建筑地面纹理</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>修理金子消耗</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>购买时间间隔</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>建筑升级</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
         <is>
           <t>武器类型</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>可建造建筑</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>建造时间</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>售出单位</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>购买开始时间</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>阴影图像(单位)</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
         <is>
           <t>编辑器后缀</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>动画伤害点</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>阴影图像(建筑)</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>攻击 2 - 投射物图像</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>攻击武器声音</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>射弹弧度</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>射弹速率</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>攻击 2 - 射弹速率</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>攻击 2 - 攻击类型</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>生命回复类型</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>动画回复点</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>护甲类型</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
         <is>
           <t>伤害骰子数量</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>最小高度</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
         <is>
           <t>转身速度</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>使用科技</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>魔法回复</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>默认主动技能</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>黄金奖励 - 骰子数量</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
         <is>
           <t>穿透伤害距离</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>攻击范围</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>攻击 2 - 攻击范围</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>图标 - 计分屏</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>动画 - 行走速度</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>允许攻击模式</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>称谓</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>射弹自导允许</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>主动攻击范围</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>死亡类型</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
         <is>
           <t>动画 - 跑步速度</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>黄金奖励 - 骰子面数</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
         <is>
           <t>提示工具 -重生</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>称谓数量</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>生命回复</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>单位声音设置</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>需求 - 等级 3</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>需求 - 等级 2</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>修理木材消耗</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>要求动画名 - 附加动画</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>伤害骰子面数</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>攻击间隔2</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>碰撞体积</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>黄金奖励 - 基础值</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>动画 - 魔法施放回复</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
         <is>
           <t>穿透伤害范围</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>木材奖励 - 基础值</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>是一个建筑</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
         <is>
           <t>动画 - 魔法施放点</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>编辑器附加数据</t>
         </is>
@@ -728,415 +824,495 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>fmade</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Requires</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Requirescount</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Trains</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>abilList</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>heroAbilList</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>spd</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>fused</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>reptm</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>pathTex</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>targs1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Missileart_1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>atkType1</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>animProps</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>mana0</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>manaN</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>movetp</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>armor</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>scale</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>STRplus</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>AGIplus</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>INTplus</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>moveHeight</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>Awakentip</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>sight</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
         <is>
           <t>nsight</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>modelScale</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>Buttonpos_1</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Buttonpos_2</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>stockMax</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>uberSplat</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>goldRep</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>stockRegen</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Upgrade</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>weapTp1</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Builds</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>bldtm</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>Sellunits</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>stockStart</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>unitShadow</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>EditorSuffix</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>dmgpt1</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>buildingShadow</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>Missileart_2</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>weapType1</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>Missilearc_1</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>Missilespeed_1</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>Missilespeed_2</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>atkType2</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>regenType</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>backSw1</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>defType</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
         <is>
           <t>dice1</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>moveFloor</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
         <is>
           <t>turnRate</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>upgrades</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>regenMana</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>bountydice</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>spillDist1</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>rangeN1</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>rangeN2</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>ScoreScreenIcon</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>weapsOn</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>Propernames</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>MissileHoming_1</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>acquire</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>deathType</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>bountysides</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
         <is>
           <t>Revivetip</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>nameCount</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>regenHP</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>unitSound</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>Requires2</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>Requires1</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>lumberRep</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>Attachmentanimprops</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>sides1</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>cool2</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>collision</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>bountyplus</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>castbsw</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>spillRadius1</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>lumberbountyplus</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>isbldg</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
         <is>
           <t>castpt</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>W2LObject</t>
         </is>
@@ -1173,32 +1349,32 @@
           <t>Ecen</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Ecen</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Aneu,Avul,Apit</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="BC3" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
           <t>Ecen</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
         <is>
           <t>"XC":"商店NPC.xlsx  【商店npc.uobj】  "</t>
         </is>
@@ -1220,70 +1396,92 @@
           <t>召唤丛林守护者(|cffffcc00K|r)</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>TALT</t>
         </is>
       </c>
-      <c r="Q4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>Ault,AInv</t>
         </is>
       </c>
-      <c r="W4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3600.0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="BR4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
         <is>
           <t>Rema</t>
         </is>
       </c>
-      <c r="CG4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
         <is>
           <t>TWN3,TALT</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CX4" t="inlineStr">
         <is>
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="CR4" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="CT4" t="inlineStr">
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1300,57 +1498,77 @@
           <t>Emoo</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>Adtg,AInv,Ault</t>
         </is>
       </c>
-      <c r="X5" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1100.0</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
           <t>Reib</t>
         </is>
       </c>
-      <c r="BV5" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CO5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CT5" t="inlineStr">
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1367,42 +1585,52 @@
           <t>Ewar</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>A0DB,AInv,Ault</t>
         </is>
       </c>
-      <c r="X6" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="BR6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
         <is>
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="CG6" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CP6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="CT6" t="inlineStr">
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1419,46 +1647,62 @@
           <t>Ewrd</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>A044,AInv,Ault</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="BE7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
         <is>
           <t>（玛维）</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="BS7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>5.0</v>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="CT7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1490,17 +1734,25 @@
           <t>一名优秀的战士，但由于偷学禁招“水月斩”被封印起来，解救她，她就会为您效力。解救她需要500点蓝。</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>400.0</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1512,155 +1764,197 @@
           <t>Units\Naga\NagaSummoner\NagaSummoner.mdl</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>A09V,AInv</t>
         </is>
       </c>
-      <c r="V8" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>ground,ward,structure,debris,item</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>.mdl</t>
         </is>
       </c>
-      <c r="AD8" t="n">
-        <v>700.0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AL8" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="AU8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1500.0</v>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>Abilities\Weapons\WaterElementalMissile\WaterElementalMissile.mdl</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>MetalHeavySlice</t>
         </is>
       </c>
-      <c r="BJ8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
         <is>
           <t>spells</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>Rnam,Rnat,Rguv</t>
         </is>
       </c>
-      <c r="BV8" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNSeaWitch.blp</t>
         </is>
       </c>
-      <c r="BZ8" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
         <is>
           <t>索菲</t>
         </is>
       </c>
-      <c r="CC8" t="n">
-        <v>800.0</v>
-      </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="CG8" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
         <is>
           <t>NagaSiren</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CX8" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CL8" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="CT8" t="inlineStr">
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1682,65 +1976,87 @@
           <t>黑暗骑士</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>350.0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AF9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>horse</t>
         </is>
       </c>
-      <c r="AM9" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="AT9" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="BR9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="BS9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
         <is>
           <t>黑暗骑士</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="CG9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>10.0</v>
-      </c>
       <c r="CT9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1772,11 +2088,15 @@
           <t>支援型英雄，非常擅长强劲的火力输出，有着高超的射击技巧，但很依赖装备</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.4</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1788,193 +2108,257 @@
           <t>Units\Critters\Marine\Marine.mdl</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>TALT</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>A09X,A09P</t>
         </is>
       </c>
-      <c r="U10" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="Y10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>ground,ward,structure,tree,debris,item,air</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Abilities\Weapons\Rifle\RifleImpact.mdl</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AD10" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AK10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>155.0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>155.0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>55.0</v>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AT10" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.0</v>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
           <t>mline</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BK10" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="BS10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
         <is>
           <t>A0AM</t>
         </is>
       </c>
-      <c r="BU10" t="n">
-        <v>150.0</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNMarine.blp</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>掉队士兵</t>
         </is>
       </c>
-      <c r="CB10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
         <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>Uther</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>mechanical</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>TWN3,TALT</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CX10" t="inlineStr">
         <is>
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="CN10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="CT10" t="inlineStr">
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2006,90 +2390,112 @@
           <t>半神宙斯……</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4.0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNAvatar.blp</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Apg2,AInv</t>
         </is>
       </c>
-      <c r="V11" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AB11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>alternate</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>复活宙斯(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AU11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BX11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNAvatar.blp</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>宙斯</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>复活宙斯(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>Muradin</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CX11" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CT11" t="inlineStr">
+      <c r="DJ11" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2111,43 +2517,57 @@
           <t>战士型英雄，特别擅长于冲锋陷阵。最终技能：狂暴矮人</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="BR12" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
         <is>
           <t>Rhan,Rhla</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CW12" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CX12" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CT12" t="inlineStr">
+      <c r="DJ12" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2169,88 +2589,122 @@
           <t>娜迦女海巫(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>400.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AA13" t="inlineStr">
+          <t>A01B,A09V,AInv</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>A0LS,A0E1,A075,AEar,AEsf</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>pierce</t>
         </is>
       </c>
-      <c r="AD13" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1500.0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>3.0</v>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
           <t>Rguv,R001</t>
         </is>
       </c>
-      <c r="BV13" t="n">
-        <v>900.0</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CT13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CW13" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CK13" t="inlineStr">
+      <c r="CX13" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CL13" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="CT13" t="inlineStr">
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="DC13" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="DJ13" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2282,156 +2736,2603 @@
           <t>服部半藏</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ReplaceableTextures\CommandButtons\BTNChaosBlademaster.blp</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>units\demon\HeroChaosBladeMaster\HeroChaosBladeMaster.mdl</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>AInv,A0PD</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Flesh</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>(|cffffcc00X|r)复活服部半藏</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>(剑魔附身)</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>Robs,Roar</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>UI\Glues\ScoreScreen\scorescreen-hero-chaosblademaster.blp</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
+      </c>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>服部半藏</t>
+        </is>
+      </c>
+      <c r="CP14" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>(|cffffcc00X|r)复活服部半藏</t>
+        </is>
+      </c>
+      <c r="CS14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CT14" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="CU14" t="inlineStr">
+        <is>
+          <t>HeroBladeMaster</t>
+        </is>
+      </c>
+      <c r="CV14" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="CZ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DA14" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="DI14" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="DJ14" t="inlineStr">
+        <is>
+          <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Q1i1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hpal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>近战力量英雄</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>units\human\HeroPaladin\HeroPaladin.mdx</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="AL15" t="n">
         <v>1.0</v>
       </c>
-      <c r="J14" t="n">
+      <c r="AM15" t="n">
         <v>1.0</v>
       </c>
-      <c r="L14" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ReplaceableTextures\CommandButtons\BTNChaosBlademaster.blp</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>units\demon\HeroChaosBladeMaster\HeroChaosBladeMaster.mdl</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>AInv,A0PD</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="AE14" t="n">
+      <c r="AN15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW15" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>950.0</v>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG15" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CS15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CT15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CU15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CX15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DA15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DE15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DI15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Q1i2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Emoo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>远程力量英雄</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>units\nightelf\HeroMoonPriestess\HeroMoonPriestess.mdx</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW16" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
+        <v>950.0</v>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG16" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CN16" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CS16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CT16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CU16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CX16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DA16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DE16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DI16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q1i3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hpal</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>近战敏捷英雄</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>units\human\HeroPaladin\HeroPaladin.mdx</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW17" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>950.0</v>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG17" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CL17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CN17" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CS17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CT17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CU17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CX17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DA17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DE17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DI17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q1i4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Emoo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>远程敏捷英雄</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>units\nightelf\HeroMoonPriestess\HeroMoonPriestess.mdx</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW18" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
+        <v>950.0</v>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG18" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CL18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CN18" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CS18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CT18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CU18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CX18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DA18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DE18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DI18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q1i5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hpal</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>近战智力英雄</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>units\human\HeroPaladin\HeroPaladin.mdx</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW19" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
+        <v>950.0</v>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG19" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CL19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CN19" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CS19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CU19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CX19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DA19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DE19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DI19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q1i6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Emoo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>远程智力英雄</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>units\nightelf\HeroMoonPriestess\HeroMoonPriestess.mdx</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW20" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>950.0</v>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG20" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CL20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CN20" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CS20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CT20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CU20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CX20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DA20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DE20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DI20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>q1i7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>hfoo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>近战单位</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AW21" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CE21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="CN21" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CO21" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CT21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DA21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>q1i8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>earc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>远程单位</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>ground,structure,air,item,ward</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AW22" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CE22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="CN22" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CO22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="CQ22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CT22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DA22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>q1i9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>hfoo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NPC单位</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>10000.0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>units\human\Jaina\Jaina.mdx</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Aneu,Asid,Avul,Asud,Apit</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW23" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CK23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>q1ia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>hfoo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NPC飞行单位</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>10000.0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>units\human\Jaina\Jaina.mdx</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Aneu,Asid,Avul,Asud,Apit</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>fly</t>
+        </is>
+      </c>
+      <c r="AW24" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CK24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>q1ib</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>hpea</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>宝宝助手</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ReplaceableTextures\CommandButtons\BTNSnowOwl.blp</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>units\critters\SnowOwl\SnowOwl.mdx</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Avul,AInv</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>522.0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>fly</t>
+        </is>
+      </c>
+      <c r="AU25" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BZ25" t="n">
         <v>90.0</v>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>Flesh</t>
-        </is>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>AGI</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>(|cffffcc00X|r)复活服部半藏</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>(剑魔附身)</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="BP14" t="n">
+      <c r="CA25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CC25" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CU25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DC25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI25" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>q1ic</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hgtw</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>防御塔</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>3.0</v>
       </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>Robs,Roar</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>UI\Glues\ScoreScreen\scorescreen-hero-chaosblademaster.blp</t>
-        </is>
-      </c>
-      <c r="BY14" t="n">
-        <v>290.0</v>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>服部半藏</t>
-        </is>
-      </c>
-      <c r="CD14" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>(|cffffcc00X|r)复活服部半藏</t>
-        </is>
-      </c>
-      <c r="CF14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="CH14" t="inlineStr">
-        <is>
-          <t>HeroBladeMaster</t>
-        </is>
-      </c>
-      <c r="CI14" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="CM14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CN14" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="CT14" t="inlineStr">
-        <is>
-          <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
-        </is>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW26" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BI26" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CY26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>q1id</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>hwtw</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>哨塔</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW27" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CY27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI27" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>q1ie</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>hwtw</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>哨塔无路径</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW28" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BO28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CY28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI28" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>q1if</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ngol</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>金矿</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Agld</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>PathTextures\4x4SimpleSolid.tga</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>HSMA</t>
+        </is>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BI29" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="BO29" t="inlineStr">
+        <is>
+          <t>BuildingShadowSmall</t>
+        </is>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CV29" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="CY29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>q1ig</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>hdhw</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[$ST]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>飞行单位</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>amph</t>
+        </is>
+      </c>
+      <c r="AW30" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DE30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/单位数据.xlsx
+++ b/xlsx/单位数据.xlsx
@@ -78,9 +78,9 @@
     <col min="18" max="18" width="23.8046875" customWidth="true"/>
     <col min="19" max="19" width="10.9609375" customWidth="true"/>
     <col min="20" max="20" width="40.3671875" customWidth="true"/>
-    <col min="21" max="21" width="42.15234375" customWidth="true"/>
+    <col min="21" max="21" width="19.85546875" customWidth="true"/>
     <col min="22" max="22" width="8.8828125" customWidth="true"/>
-    <col min="23" max="23" width="10.28515625" customWidth="true"/>
+    <col min="23" max="23" width="9.33984375" customWidth="true"/>
     <col min="24" max="24" width="10.15234375" customWidth="true"/>
     <col min="25" max="25" width="11.12890625" customWidth="true"/>
     <col min="26" max="26" width="52.07421875" customWidth="true"/>
@@ -1396,75 +1396,60 @@
           <t>召唤丛林守护者(|cffffcc00K|r)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G4" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.0</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>TALT</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="R4" t="n">
+        <v>3.0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>Ault,AInv</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>5.0</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
+      <c r="AG4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>3600.0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>180.0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
           <t>Rema</t>
         </is>
       </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="CT4" t="n">
+        <v>4.0</v>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
@@ -1476,10 +1461,8 @@
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
+      <c r="DG4" t="n">
+        <v>2000.0</v>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
@@ -1498,60 +1481,47 @@
           <t>Emoo</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="J5" t="n">
+        <v>2.25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>Adtg,AInv,Ault</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1100.0</t>
-        </is>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1100.0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
           <t>Reib</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="CG5" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>10.0</v>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
@@ -1563,10 +1533,8 @@
           <t>TWN2</t>
         </is>
       </c>
-      <c r="DB5" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="DB5" t="n">
+        <v>2.25</v>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
@@ -1585,35 +1553,32 @@
           <t>Ewar</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="I6" t="n">
+        <v>1.0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>A0DB,AInv,Ault</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>100.0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="CT6" t="n">
+        <v>10.0</v>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
@@ -1625,10 +1590,8 @@
           <t>TWN2</t>
         </is>
       </c>
-      <c r="DC6" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="DC6" t="n">
+        <v>30.0</v>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
@@ -1647,40 +1610,33 @@
           <t>Ewrd</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="I7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>A044,AInv,Ault</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.0</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
@@ -1692,15 +1648,11 @@
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="CC7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>5.0</v>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
@@ -1734,25 +1686,17 @@
           <t>一名优秀的战士，但由于偷学禁招“水月斩”被封印起来，解救她，她就会为您效力。解救她需要500点蓝。</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
+      <c r="H8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>600.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>400.0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1774,15 +1718,16 @@
           <t>A09V,AInv</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>320.0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.0</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1794,60 +1739,42 @@
           <t>.mdl</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="AF8" t="n">
+        <v>700.0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>100.0</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2.0</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
+      <c r="AY8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1500.0</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
@@ -1864,20 +1791,14 @@
           <t>MetalHeavySlice</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
+      <c r="BR8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>2000.0</v>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
@@ -1889,40 +1810,32 @@
           <t>Rnam,Rnat,Rguv</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
+      <c r="CG8" t="n">
+        <v>200.0</v>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNSeaWitch.blp</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="CK8" t="n">
+        <v>3.0</v>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
           <t>索菲</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
-        <is>
-          <t>800.0</t>
-        </is>
+      <c r="CN8" t="n">
+        <v>800.0</v>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="CT8" t="n">
+        <v>2.0</v>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
@@ -1939,20 +1852,14 @@
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="DB8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="DC8" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="CY8" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>30.0</v>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
@@ -1976,65 +1883,52 @@
           <t>黑暗骑士</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>350.0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="F9" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>350.0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>100.0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>horse</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="AO9" t="n">
+        <v>3.0</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>500.0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CC9" t="n">
+        <v>1.0</v>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
@@ -2046,15 +1940,11 @@
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="CT9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>10.0</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
@@ -2088,15 +1978,11 @@
           <t>支援型英雄，非常擅长强劲的火力输出，有着高超的射击技巧，但很依赖装备</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+      <c r="H10" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2113,30 +1999,27 @@
           <t>TALT</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="R10" t="n">
+        <v>3.0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>A09X,A09P</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.0</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -2153,155 +2036,107 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
+      <c r="AF10" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>400.0</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>55.0</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.0</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
           <t>mline</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
+      <c r="BK10" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.17</v>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="BS10" t="n">
+        <v>10000.0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CC10" t="n">
+        <v>0.0</v>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
           <t>A0AM</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
+      <c r="CF10" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>600.0</v>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
@@ -2313,15 +2148,11 @@
           <t>掉队士兵</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CN10" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="CM10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1000.0</v>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
@@ -2348,15 +2179,11 @@
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
+      <c r="DA10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>50.0</v>
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
@@ -2390,20 +2217,14 @@
           <t>半神宙斯……</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G11" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2415,55 +2236,44 @@
           <t>Apg2,AInv</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>40.0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>alternate</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="AG11" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.0</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>复活宙斯(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="AY11" t="n">
+        <v>1.5</v>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
@@ -2517,40 +2327,31 @@
           <t>战士型英雄，特别擅长于冲锋陷阵。最终技能：狂暴矮人</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
+      <c r="F12" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>80.0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
@@ -2589,15 +2390,11 @@
           <t>娜迦女海巫(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
+      <c r="K13" t="n">
+        <v>600.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>400.0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2606,83 +2403,57 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>A0LS,A0E1,A075,AEar,AEsf</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>320.0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5.0</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>pierce</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="AF13" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>3.0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
           <t>Rguv,R001</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>900.0</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CN13" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CT13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CG13" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>1.0</v>
       </c>
       <c r="CW13" t="inlineStr">
         <is>
@@ -2694,15 +2465,11 @@
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CY13" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="DC13" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="CY13" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>30.0</v>
       </c>
       <c r="DJ13" t="inlineStr">
         <is>
@@ -2736,20 +2503,14 @@
           <t>服部半藏</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
+      <c r="I14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>200.0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2766,85 +2527,66 @@
           <t>AInv,A0PD</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>320.0</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>40.0</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
+      <c r="AG14" t="n">
+        <v>90.0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
           <t>Flesh</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="AJ14" t="n">
+        <v>1.5</v>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
+      <c r="AL14" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.7</v>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
+      <c r="BK14" t="n">
+        <v>180.0</v>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
@@ -2856,10 +2598,8 @@
           <t>always</t>
         </is>
       </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="BY14" t="n">
+        <v>3.0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
@@ -2871,35 +2611,27 @@
           <t>UI\Glues\ScoreScreen\scorescreen-hero-chaosblademaster.blp</t>
         </is>
       </c>
-      <c r="CJ14" t="inlineStr">
-        <is>
-          <t>290.0</t>
-        </is>
+      <c r="CJ14" t="n">
+        <v>290.0</v>
       </c>
       <c r="CL14" t="inlineStr">
         <is>
           <t>服部半藏</t>
         </is>
       </c>
-      <c r="CP14" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
+      <c r="CP14" t="n">
+        <v>300.0</v>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="CS14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CT14" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="CS14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.25</v>
       </c>
       <c r="CU14" t="inlineStr">
         <is>
@@ -2916,15 +2648,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="DA14" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="DI14" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="DA14" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.3</v>
       </c>
       <c r="DJ14" t="inlineStr">
         <is>

--- a/xlsx/单位数据.xlsx
+++ b/xlsx/单位数据.xlsx
@@ -64,7 +64,7 @@
     <col min="4" max="4" width="70.3125" customWidth="true"/>
     <col min="5" max="5" width="70.3125" customWidth="true"/>
     <col min="6" max="6" width="16.62109375" customWidth="true"/>
-    <col min="7" max="7" width="14.078125" customWidth="true"/>
+    <col min="7" max="7" width="11.234375" customWidth="true"/>
     <col min="8" max="8" width="9.33984375" customWidth="true"/>
     <col min="9" max="9" width="13.1328125" customWidth="true"/>
     <col min="10" max="10" width="10.0390625" customWidth="true"/>
@@ -79,7 +79,7 @@
     <col min="19" max="19" width="40.3671875" customWidth="true"/>
     <col min="20" max="20" width="19.85546875" customWidth="true"/>
     <col min="21" max="21" width="8.8828125" customWidth="true"/>
-    <col min="22" max="22" width="10.28515625" customWidth="true"/>
+    <col min="22" max="22" width="9.33984375" customWidth="true"/>
     <col min="23" max="23" width="10.15234375" customWidth="true"/>
     <col min="24" max="24" width="11.12890625" customWidth="true"/>
     <col min="25" max="25" width="52.07421875" customWidth="true"/>
@@ -1312,10 +1312,8 @@
           <t>召唤丛林守护者(|cffffcc00K|r)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
+      <c r="G3" t="n">
+        <v>200.0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1327,10 +1325,8 @@
           <t>TALT</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="Q3" t="n">
+        <v>3.0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1342,40 +1338,30 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="W3" t="n">
+        <v>5.0</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="AF3" t="n">
+        <v>100.0</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
+      <c r="BA3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3600.0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>180.0</v>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
@@ -1397,10 +1383,8 @@
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
+      <c r="DE3" t="n">
+        <v>2000.0</v>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
@@ -1434,40 +1418,30 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="X4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>100.0</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>1100.0</t>
-        </is>
+      <c r="BQ4" t="n">
+        <v>1100.0</v>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
           <t>Reib</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="CE4" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>1000.0</v>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
@@ -1526,15 +1500,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="X5" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>100.0</v>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
@@ -1598,20 +1568,14 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="V6" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>100.0</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1680,15 +1644,11 @@
           <t>4.0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
+      <c r="K7" t="n">
+        <v>600.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>400.0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1715,15 +1675,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>320.0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="V7" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5.0</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1735,25 +1691,19 @@
           <t>.mdl</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="AE7" t="n">
+        <v>700.0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>100.0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>16.0</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1780,15 +1730,11 @@
           <t>1.2</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
+      <c r="BA7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1500.0</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -1810,15 +1756,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
+      <c r="BQ7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>2000.0</v>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
@@ -1830,20 +1772,16 @@
           <t>Rnam,Rnat,Rguv</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
+      <c r="CE7" t="n">
+        <v>200.0</v>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNSeaWitch.blp</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="CI7" t="n">
+        <v>3.0</v>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
@@ -1880,10 +1818,8 @@
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
+      <c r="CW7" t="n">
+        <v>500.0</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -1917,10 +1853,8 @@
           <t>黑暗骑士</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="F8" t="n">
+        <v>30.0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1932,25 +1866,17 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>350.0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="U8" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>350.0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>100.0</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1967,10 +1893,8 @@
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
+      <c r="AW8" t="n">
+        <v>500.0</v>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
@@ -1997,10 +1921,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="CY8" t="n">
+        <v>10.0</v>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
@@ -2059,10 +1981,8 @@
           <t>TALT</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="Q9" t="n">
+        <v>3.0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2074,20 +1994,14 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="U9" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>5.0</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -2104,30 +2018,22 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
+      <c r="AE9" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>400.0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AL9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.0</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -2144,136 +2050,112 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
+      <c r="AQ9" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>55.0</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AW9" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>mline</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BQ9" t="n">
+        <v>10000.0</v>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Rguv</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>A0AM</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="n">
+        <v>600.0</v>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>ReplaceableTextures\CommandButtons\BTNMarine.blp</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>掉队士兵</t>
+        </is>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CL9" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>mline</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>Rguv</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>A0AM</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>ReplaceableTextures\CommandButtons\BTNMarine.blp</t>
-        </is>
-      </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>掉队士兵</t>
-        </is>
-      </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
       <c r="CP9" t="inlineStr">
         <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
@@ -2299,10 +2181,8 @@
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CY9" t="n">
+        <v>1.0</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
@@ -2341,10 +2221,8 @@
           <t>半神宙斯……</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
+      <c r="G10" t="n">
+        <v>300.0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2371,40 +2249,28 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="V10" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>40.0</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>alternate</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
+      <c r="AF10" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>24.0</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2473,15 +2339,11 @@
           <t>战士型英雄，特别擅长于冲锋陷阵。最终技能：狂暴矮人</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
+      <c r="F11" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>300.0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2498,20 +2360,14 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
+      <c r="V11" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>80.0</v>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
@@ -2550,15 +2406,11 @@
           <t>娜迦女海巫(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
+      <c r="K12" t="n">
+        <v>600.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>400.0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2570,81 +2422,61 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>320.0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="V12" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.0</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
           <t>pierce</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>Rguv,R001</t>
+        </is>
+      </c>
+      <c r="CE12" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>Rguv,R001</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>900.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CL12" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="CU12" t="inlineStr">
         <is>
           <t>TWN3</t>
@@ -2655,10 +2487,8 @@
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CW12" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
+      <c r="CW12" t="n">
+        <v>500.0</v>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
@@ -2707,10 +2537,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
+      <c r="L13" t="n">
+        <v>200.0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2732,30 +2560,22 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>320.0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="U13" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>40.0</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
+      <c r="AF13" t="n">
+        <v>90.0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2772,20 +2592,14 @@
           <t>AGI</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
+      <c r="AK13" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>16.0</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2807,10 +2621,8 @@
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
+      <c r="BJ13" t="n">
+        <v>180.0</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -2822,10 +2634,8 @@
           <t>always</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="BW13" t="n">
+        <v>3.0</v>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
@@ -2857,10 +2667,8 @@
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="CQ13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CQ13" t="n">
+        <v>1.0</v>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
@@ -2882,10 +2690,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY13" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="CY13" t="n">
+        <v>10.0</v>
       </c>
       <c r="DG13" t="inlineStr">
         <is>
@@ -2934,10 +2740,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="Q14" t="n">
+        <v>0.0</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2949,15 +2753,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>410.0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V14" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2974,30 +2774,22 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AE14" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AK14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.0</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -3019,15 +2811,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
+      <c r="AV14" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3000.0</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
@@ -3044,20 +2832,16 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>950.0</t>
-        </is>
+      <c r="BQ14" t="n">
+        <v>950.0</v>
       </c>
       <c r="BU14" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="BW14" t="n">
+        <v>1.0</v>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
@@ -3069,35 +2853,29 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
+      <c r="CE14" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CL14" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CJ14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CK14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CL14" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
       <c r="CP14" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CQ14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CQ14" t="n">
+        <v>1.0</v>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
@@ -3119,10 +2897,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CY14" t="n">
+        <v>1.0</v>
       </c>
       <c r="DC14" t="inlineStr">
         <is>
@@ -3166,10 +2942,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="Q15" t="n">
+        <v>0.0</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -3181,15 +2955,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>410.0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V15" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -3206,10 +2976,8 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AE15" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -3221,20 +2989,14 @@
           <t>STR</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AK15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.0</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -3256,35 +3018,27 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
+      <c r="AV15" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3000.0</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>950.0</t>
-        </is>
+      <c r="BQ15" t="n">
+        <v>950.0</v>
       </c>
       <c r="BU15" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="BW15" t="n">
+        <v>1.0</v>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
@@ -3296,30 +3050,26 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
+      <c r="CE15" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CJ15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CL15" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
       <c r="CP15" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CQ15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CQ15" t="n">
+        <v>1.0</v>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
@@ -3341,10 +3091,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CY15" t="n">
+        <v>1.0</v>
       </c>
       <c r="DC15" t="inlineStr">
         <is>
@@ -3393,10 +3141,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="Q16" t="n">
+        <v>0.0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3408,15 +3154,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>410.0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V16" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -3433,10 +3175,8 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AE16" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -3448,20 +3188,14 @@
           <t>AGI</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AK16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.0</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -3483,15 +3217,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
+      <c r="AV16" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3000.0</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
@@ -3508,20 +3238,16 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>950.0</t>
-        </is>
+      <c r="BQ16" t="n">
+        <v>950.0</v>
       </c>
       <c r="BU16" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="BW16" t="n">
+        <v>1.0</v>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
@@ -3533,35 +3259,29 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
+      <c r="CE16" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CL16" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CJ16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CK16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CL16" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
       <c r="CP16" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CQ16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CQ16" t="n">
+        <v>1.0</v>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
@@ -3583,10 +3303,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CY16" t="n">
+        <v>1.0</v>
       </c>
       <c r="DC16" t="inlineStr">
         <is>
@@ -3630,10 +3348,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="Q17" t="n">
+        <v>0.0</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -3645,15 +3361,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>410.0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V17" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -3670,30 +3382,22 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AE17" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AK17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.0</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3715,35 +3419,27 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
+      <c r="AV17" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3000.0</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>950.0</t>
-        </is>
+      <c r="BQ17" t="n">
+        <v>950.0</v>
       </c>
       <c r="BU17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="BW17" t="n">
+        <v>1.0</v>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
@@ -3755,30 +3451,26 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
+      <c r="CE17" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CL17" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CJ17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CL17" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
       <c r="CP17" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CQ17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CQ17" t="n">
+        <v>1.0</v>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
@@ -3800,10 +3492,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CY17" t="n">
+        <v>1.0</v>
       </c>
       <c r="DC17" t="inlineStr">
         <is>
@@ -3852,10 +3542,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="Q18" t="n">
+        <v>0.0</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3867,15 +3555,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>410.0</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V18" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -3892,10 +3576,8 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AE18" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3907,20 +3589,14 @@
           <t>INT</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AK18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
@@ -3942,15 +3618,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
+      <c r="AV18" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3000.0</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
@@ -3967,20 +3639,16 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>950.0</t>
-        </is>
+      <c r="BQ18" t="n">
+        <v>950.0</v>
       </c>
       <c r="BU18" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="BW18" t="n">
+        <v>1.0</v>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
@@ -3992,35 +3660,29 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
+      <c r="CE18" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CK18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="CL18" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CJ18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CK18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CL18" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
       <c r="CP18" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CQ18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CQ18" t="n">
+        <v>1.0</v>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
@@ -4042,10 +3704,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CY18" t="n">
+        <v>1.0</v>
       </c>
       <c r="DC18" t="inlineStr">
         <is>
@@ -4089,10 +3749,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="Q19" t="n">
+        <v>0.0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -4104,15 +3762,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>410.0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V19" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -4129,10 +3783,8 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AE19" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -4144,20 +3796,14 @@
           <t>INT</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="AK19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.0</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -4179,35 +3825,27 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
+      <c r="AV19" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3000.0</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>950.0</t>
-        </is>
+      <c r="BQ19" t="n">
+        <v>950.0</v>
       </c>
       <c r="BU19" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="BW19" t="n">
+        <v>1.0</v>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
@@ -4219,30 +3857,26 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
+      <c r="CE19" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CL19" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CJ19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CL19" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
       <c r="CP19" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CQ19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CQ19" t="n">
+        <v>1.0</v>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
@@ -4264,10 +3898,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="CY19" t="n">
+        <v>1.0</v>
       </c>
       <c r="DC19" t="inlineStr">
         <is>
@@ -4368,45 +4000,33 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="F21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100.0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="K21" t="n">
+        <v>0.0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="U21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -4418,105 +4038,81 @@
           <t>amph</t>
         </is>
       </c>
-      <c r="AV21" t="inlineStr">
+      <c r="AV21" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="BQ21" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="CL21" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>900.0</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>hero</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="CL21" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CM21" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="CO21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CM21" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>0.0</v>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DB21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CY21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>0.0</v>
       </c>
       <c r="DC21" t="inlineStr">
         <is>
@@ -4555,45 +4151,33 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="F22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100.0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="K22" t="n">
+        <v>0.0</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="U22" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -4605,90 +4189,68 @@
           <t>amph</t>
         </is>
       </c>
-      <c r="AV22" t="inlineStr">
+      <c r="AV22" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CC22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="CL22" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>hero</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="CL22" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="CM22" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="CO22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CM22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>0.0</v>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DB22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CY22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0.0</v>
       </c>
       <c r="DC22" t="inlineStr">
         <is>
@@ -4727,10 +4289,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
+      <c r="G23" t="n">
+        <v>10000.0</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -4742,60 +4302,44 @@
           <t>Aneu,Asid,Avul,Asud,Apit</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="V23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>5.0</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="AV23" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5.0</v>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CI23" t="n">
+        <v>0.0</v>
       </c>
       <c r="DC23" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DF23" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="DF23" t="n">
+        <v>1.0</v>
       </c>
       <c r="DG23" t="inlineStr">
         <is>
@@ -4829,10 +4373,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
+      <c r="G24" t="n">
+        <v>10000.0</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -4844,50 +4386,38 @@
           <t>Aneu,Asid,Avul,Asud,Apit</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
           <t>fly</t>
         </is>
       </c>
-      <c r="AV24" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="AV24" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1000.0</v>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CI24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CI24" t="n">
+        <v>0.0</v>
       </c>
       <c r="DC24" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DF24" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="DF24" t="n">
+        <v>1.0</v>
       </c>
       <c r="DG24" t="inlineStr">
         <is>
@@ -4916,10 +4446,8 @@
           <t>宝宝助手</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="G25" t="n">
+        <v>100.0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -4936,30 +4464,22 @@
           <t>Avul,AInv</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>522.0</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="V25" t="n">
+        <v>522.0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="AE25" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000.0</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -4971,15 +4491,11 @@
           <t>240.0</t>
         </is>
       </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="AV25" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1000.0</v>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
@@ -5006,10 +4522,8 @@
           <t>10.0</t>
         </is>
       </c>
-      <c r="CI25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CI25" t="n">
+        <v>0.0</v>
       </c>
       <c r="CL25" t="inlineStr">
         <is>
@@ -5063,20 +4577,14 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="G26" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -5088,45 +4596,33 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="X26" t="n">
+        <v>3.0</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="AV26" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.0</v>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CW26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CW26" t="n">
+        <v>0.0</v>
       </c>
       <c r="DC26" t="inlineStr">
         <is>
@@ -5165,60 +4661,44 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="G27" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="BC27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="X27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0.0</v>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="BH27" t="n">
+        <v>3.0</v>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CW27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CW27" t="n">
+        <v>0.0</v>
       </c>
       <c r="DC27" t="inlineStr">
         <is>
@@ -5257,60 +4737,46 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="G28" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="X28" t="n">
+        <v>3.0</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="AV28" t="n">
+        <v>1000.0</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="BC28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="BC28" t="n">
+        <v>0.0</v>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="BH28" t="n">
+        <v>3.0</v>
       </c>
       <c r="BM28" t="inlineStr">
         <is>
@@ -5322,10 +4788,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CW28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="CW28" t="n">
+        <v>0.0</v>
       </c>
       <c r="DC28" t="inlineStr">
         <is>
@@ -5359,20 +4823,16 @@
           <t>金矿</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="G29" t="n">
+        <v>100.0</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
           <t>Agld</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="X29" t="n">
+        <v>3.0</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -5384,25 +4844,19 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="AV29" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="AV29" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1000.0</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
           <t>HSMA</t>
         </is>
       </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="BH29" t="n">
+        <v>3.0</v>
       </c>
       <c r="BM29" t="inlineStr">
         <is>
@@ -5456,35 +4910,27 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
+      <c r="G30" t="n">
+        <v>100.0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="W30" t="n">
+        <v>0.0</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AV30" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
+      <c r="AV30" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1000.0</v>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>

--- a/xlsx/单位数据.xlsx
+++ b/xlsx/单位数据.xlsx
@@ -63,113 +63,127 @@
     <col min="3" max="3" width="13.1328125" customWidth="true"/>
     <col min="4" max="4" width="70.3125" customWidth="true"/>
     <col min="5" max="5" width="70.3125" customWidth="true"/>
-    <col min="6" max="6" width="16.62109375" customWidth="true"/>
-    <col min="7" max="7" width="11.234375" customWidth="true"/>
-    <col min="8" max="8" width="9.33984375" customWidth="true"/>
-    <col min="9" max="9" width="13.1328125" customWidth="true"/>
-    <col min="10" max="10" width="10.0390625" customWidth="true"/>
-    <col min="11" max="11" width="14.58203125" customWidth="true"/>
-    <col min="12" max="12" width="18.96875" customWidth="true"/>
-    <col min="13" max="13" width="19.53125" customWidth="true"/>
+    <col min="6" max="6" width="21.42578125" customWidth="true"/>
+    <col min="7" max="7" width="16.62109375" customWidth="true"/>
+    <col min="8" max="8" width="14.078125" customWidth="true"/>
+    <col min="9" max="9" width="9.33984375" customWidth="true"/>
+    <col min="10" max="10" width="13.1328125" customWidth="true"/>
+    <col min="11" max="11" width="10.0390625" customWidth="true"/>
+    <col min="12" max="12" width="14.58203125" customWidth="true"/>
+    <col min="13" max="13" width="18.96875" customWidth="true"/>
     <col min="14" max="14" width="19.53125" customWidth="true"/>
-    <col min="15" max="15" width="15.4765625" customWidth="true"/>
-    <col min="16" max="16" width="17.5625" customWidth="true"/>
-    <col min="17" max="17" width="23.8046875" customWidth="true"/>
-    <col min="18" max="18" width="10.9609375" customWidth="true"/>
-    <col min="19" max="19" width="40.3671875" customWidth="true"/>
-    <col min="20" max="20" width="19.85546875" customWidth="true"/>
-    <col min="21" max="21" width="8.8828125" customWidth="true"/>
-    <col min="22" max="22" width="9.33984375" customWidth="true"/>
-    <col min="23" max="23" width="10.15234375" customWidth="true"/>
-    <col min="24" max="24" width="11.12890625" customWidth="true"/>
-    <col min="25" max="25" width="52.07421875" customWidth="true"/>
-    <col min="26" max="26" width="66.578125" customWidth="true"/>
-    <col min="27" max="27" width="19.53125" customWidth="true"/>
-    <col min="28" max="28" width="15.7421875" customWidth="true"/>
-    <col min="29" max="29" width="17.99609375" customWidth="true"/>
-    <col min="30" max="30" width="15.9609375" customWidth="true"/>
-    <col min="31" max="31" width="13.1328125" customWidth="true"/>
-    <col min="32" max="32" width="12.70703125" customWidth="true"/>
-    <col min="33" max="33" width="13.484375" customWidth="true"/>
-    <col min="34" max="34" width="11.11328125" customWidth="true"/>
-    <col min="35" max="35" width="9.31640625" customWidth="true"/>
-    <col min="36" max="36" width="13.6328125" customWidth="true"/>
-    <col min="37" max="37" width="9.33984375" customWidth="true"/>
-    <col min="38" max="38" width="9.33984375" customWidth="true"/>
-    <col min="39" max="39" width="9.33984375" customWidth="true"/>
-    <col min="40" max="40" width="15.02734375" customWidth="true"/>
-    <col min="41" max="41" width="15.02734375" customWidth="true"/>
-    <col min="42" max="42" width="15.02734375" customWidth="true"/>
-    <col min="43" max="43" width="11.60546875" customWidth="true"/>
-    <col min="44" max="44" width="11.60546875" customWidth="true"/>
-    <col min="45" max="45" width="11.60546875" customWidth="true"/>
-    <col min="46" max="46" width="20.296875" customWidth="true"/>
-    <col min="47" max="47" width="35.6640625" customWidth="true"/>
-    <col min="48" max="48" width="15.3984375" customWidth="true"/>
-    <col min="49" max="49" width="15.3984375" customWidth="true"/>
-    <col min="50" max="50" width="19.21484375" customWidth="true"/>
-    <col min="51" max="51" width="21.359375" customWidth="true"/>
-    <col min="52" max="52" width="21.359375" customWidth="true"/>
-    <col min="53" max="53" width="16.3359375" customWidth="true"/>
-    <col min="54" max="54" width="16.44140625" customWidth="true"/>
-    <col min="55" max="55" width="14.16796875" customWidth="true"/>
-    <col min="56" max="56" width="19.203125" customWidth="true"/>
-    <col min="57" max="57" width="14.80859375" customWidth="true"/>
-    <col min="58" max="58" width="15.73046875" customWidth="true"/>
-    <col min="59" max="59" width="11.234375" customWidth="true"/>
-    <col min="60" max="60" width="10.7890625" customWidth="true"/>
-    <col min="61" max="61" width="14.5625" customWidth="true"/>
-    <col min="62" max="62" width="17.04296875" customWidth="true"/>
-    <col min="63" max="63" width="19.3828125" customWidth="true"/>
-    <col min="64" max="64" width="13.5859375" customWidth="true"/>
-    <col min="65" max="65" width="34.32421875" customWidth="true"/>
-    <col min="66" max="66" width="19.53125" customWidth="true"/>
-    <col min="67" max="67" width="26.9609375" customWidth="true"/>
-    <col min="68" max="68" width="20.75" customWidth="true"/>
-    <col min="69" max="69" width="25.19140625" customWidth="true"/>
-    <col min="70" max="70" width="25.19140625" customWidth="true"/>
-    <col min="71" max="71" width="18.7109375" customWidth="true"/>
-    <col min="72" max="72" width="17.84765625" customWidth="true"/>
-    <col min="73" max="73" width="15.0859375" customWidth="true"/>
-    <col min="74" max="74" width="14.0703125" customWidth="true"/>
-    <col min="75" max="75" width="13.1328125" customWidth="true"/>
-    <col min="76" max="76" width="18.09375" customWidth="true"/>
-    <col min="77" max="77" width="15.1796875" customWidth="true"/>
-    <col min="78" max="78" width="28.48046875" customWidth="true"/>
-    <col min="79" max="79" width="19.2578125" customWidth="true"/>
+    <col min="15" max="15" width="19.53125" customWidth="true"/>
+    <col min="16" max="16" width="15.4765625" customWidth="true"/>
+    <col min="17" max="17" width="17.5625" customWidth="true"/>
+    <col min="18" max="18" width="23.8046875" customWidth="true"/>
+    <col min="19" max="19" width="10.9609375" customWidth="true"/>
+    <col min="20" max="20" width="40.3671875" customWidth="true"/>
+    <col min="21" max="21" width="19.85546875" customWidth="true"/>
+    <col min="22" max="22" width="8.8828125" customWidth="true"/>
+    <col min="23" max="23" width="10.28515625" customWidth="true"/>
+    <col min="24" max="24" width="10.15234375" customWidth="true"/>
+    <col min="25" max="25" width="11.12890625" customWidth="true"/>
+    <col min="26" max="26" width="52.07421875" customWidth="true"/>
+    <col min="27" max="27" width="66.578125" customWidth="true"/>
+    <col min="28" max="28" width="19.53125" customWidth="true"/>
+    <col min="29" max="29" width="15.7421875" customWidth="true"/>
+    <col min="30" max="30" width="17.99609375" customWidth="true"/>
+    <col min="31" max="31" width="15.9609375" customWidth="true"/>
+    <col min="32" max="32" width="12.5703125" customWidth="true"/>
+    <col min="33" max="33" width="13.1328125" customWidth="true"/>
+    <col min="34" max="34" width="12.70703125" customWidth="true"/>
+    <col min="35" max="35" width="13.484375" customWidth="true"/>
+    <col min="36" max="36" width="11.11328125" customWidth="true"/>
+    <col min="37" max="37" width="9.31640625" customWidth="true"/>
+    <col min="38" max="38" width="26.47265625" customWidth="true"/>
+    <col min="39" max="39" width="13.6328125" customWidth="true"/>
+    <col min="40" max="40" width="9.33984375" customWidth="true"/>
+    <col min="41" max="41" width="9.33984375" customWidth="true"/>
+    <col min="42" max="42" width="9.33984375" customWidth="true"/>
+    <col min="43" max="43" width="15.02734375" customWidth="true"/>
+    <col min="44" max="44" width="15.02734375" customWidth="true"/>
+    <col min="45" max="45" width="15.02734375" customWidth="true"/>
+    <col min="46" max="46" width="11.60546875" customWidth="true"/>
+    <col min="47" max="47" width="11.60546875" customWidth="true"/>
+    <col min="48" max="48" width="11.60546875" customWidth="true"/>
+    <col min="49" max="49" width="20.296875" customWidth="true"/>
+    <col min="50" max="50" width="35.6640625" customWidth="true"/>
+    <col min="51" max="51" width="15.3984375" customWidth="true"/>
+    <col min="52" max="52" width="15.3984375" customWidth="true"/>
+    <col min="53" max="53" width="19.21484375" customWidth="true"/>
+    <col min="54" max="54" width="21.359375" customWidth="true"/>
+    <col min="55" max="55" width="21.359375" customWidth="true"/>
+    <col min="56" max="56" width="16.3359375" customWidth="true"/>
+    <col min="57" max="57" width="16.44140625" customWidth="true"/>
+    <col min="58" max="58" width="14.16796875" customWidth="true"/>
+    <col min="59" max="59" width="19.203125" customWidth="true"/>
+    <col min="60" max="60" width="14.80859375" customWidth="true"/>
+    <col min="61" max="61" width="15.73046875" customWidth="true"/>
+    <col min="62" max="62" width="11.234375" customWidth="true"/>
+    <col min="63" max="63" width="10.7890625" customWidth="true"/>
+    <col min="64" max="64" width="14.5625" customWidth="true"/>
+    <col min="65" max="65" width="17.04296875" customWidth="true"/>
+    <col min="66" max="66" width="19.88671875" customWidth="true"/>
+    <col min="67" max="67" width="19.3828125" customWidth="true"/>
+    <col min="68" max="68" width="13.5859375" customWidth="true"/>
+    <col min="69" max="69" width="34.32421875" customWidth="true"/>
+    <col min="70" max="70" width="19.53125" customWidth="true"/>
+    <col min="71" max="71" width="26.9609375" customWidth="true"/>
+    <col min="72" max="72" width="20.75" customWidth="true"/>
+    <col min="73" max="73" width="25.19140625" customWidth="true"/>
+    <col min="74" max="74" width="25.19140625" customWidth="true"/>
+    <col min="75" max="75" width="16.73828125" customWidth="true"/>
+    <col min="76" max="76" width="18.7109375" customWidth="true"/>
+    <col min="77" max="77" width="17.84765625" customWidth="true"/>
+    <col min="78" max="78" width="15.0859375" customWidth="true"/>
+    <col min="79" max="79" width="14.0703125" customWidth="true"/>
     <col min="80" max="80" width="13.1328125" customWidth="true"/>
-    <col min="81" max="81" width="19.76171875" customWidth="true"/>
-    <col min="82" max="82" width="15.53125" customWidth="true"/>
-    <col min="83" max="83" width="14.74609375" customWidth="true"/>
-    <col min="84" max="84" width="18.7109375" customWidth="true"/>
-    <col min="85" max="85" width="19.53125" customWidth="true"/>
-    <col min="86" max="86" width="15.96875" customWidth="true"/>
-    <col min="87" max="87" width="15.95703125" customWidth="true"/>
-    <col min="88" max="88" width="22.1640625" customWidth="true"/>
-    <col min="89" max="89" width="27.94921875" customWidth="true"/>
+    <col min="81" max="81" width="15.96875" customWidth="true"/>
+    <col min="82" max="82" width="18.09375" customWidth="true"/>
+    <col min="83" max="83" width="15.1796875" customWidth="true"/>
+    <col min="84" max="84" width="28.48046875" customWidth="true"/>
+    <col min="85" max="85" width="15.96875" customWidth="true"/>
+    <col min="86" max="86" width="19.80859375" customWidth="true"/>
+    <col min="87" max="87" width="19.6875" customWidth="true"/>
+    <col min="88" max="88" width="19.2578125" customWidth="true"/>
+    <col min="89" max="89" width="16.91796875" customWidth="true"/>
     <col min="90" max="90" width="13.1328125" customWidth="true"/>
-    <col min="91" max="91" width="17.93359375" customWidth="true"/>
-    <col min="92" max="92" width="15.96875" customWidth="true"/>
-    <col min="93" max="93" width="20.1796875" customWidth="true"/>
-    <col min="94" max="94" width="35.6640625" customWidth="true"/>
-    <col min="95" max="95" width="19.515625" customWidth="true"/>
-    <col min="96" max="96" width="14.7734375" customWidth="true"/>
-    <col min="97" max="97" width="28.60546875" customWidth="true"/>
-    <col min="98" max="98" width="19.2109375" customWidth="true"/>
-    <col min="99" max="99" width="19.53515625" customWidth="true"/>
-    <col min="100" max="100" width="19.53515625" customWidth="true"/>
-    <col min="101" max="101" width="18.55859375" customWidth="true"/>
-    <col min="102" max="102" width="36.1015625" customWidth="true"/>
+    <col min="91" max="91" width="19.76171875" customWidth="true"/>
+    <col min="92" max="92" width="19.76171875" customWidth="true"/>
+    <col min="93" max="93" width="20.1328125" customWidth="true"/>
+    <col min="94" max="94" width="15.53125" customWidth="true"/>
+    <col min="95" max="95" width="14.74609375" customWidth="true"/>
+    <col min="96" max="96" width="18.7109375" customWidth="true"/>
+    <col min="97" max="97" width="19.53125" customWidth="true"/>
+    <col min="98" max="98" width="15.96875" customWidth="true"/>
+    <col min="99" max="99" width="15.95703125" customWidth="true"/>
+    <col min="100" max="100" width="22.1640625" customWidth="true"/>
+    <col min="101" max="101" width="27.94921875" customWidth="true"/>
+    <col min="102" max="102" width="27.5625" customWidth="true"/>
     <col min="103" max="103" width="13.1328125" customWidth="true"/>
-    <col min="104" max="104" width="11.234375" customWidth="true"/>
-    <col min="105" max="105" width="14.14453125" customWidth="true"/>
-    <col min="106" max="106" width="18.82421875" customWidth="true"/>
-    <col min="107" max="107" width="19.76171875" customWidth="true"/>
-    <col min="108" max="108" width="19.7265625" customWidth="true"/>
-    <col min="109" max="109" width="29.76171875" customWidth="true"/>
-    <col min="110" max="110" width="11.234375" customWidth="true"/>
-    <col min="111" max="111" width="17.86328125" customWidth="true"/>
-    <col min="112" max="112" width="53.546875" customWidth="true"/>
+    <col min="104" max="104" width="17.93359375" customWidth="true"/>
+    <col min="105" max="105" width="15.96875" customWidth="true"/>
+    <col min="106" max="106" width="20.1796875" customWidth="true"/>
+    <col min="107" max="107" width="35.6640625" customWidth="true"/>
+    <col min="108" max="108" width="19.515625" customWidth="true"/>
+    <col min="109" max="109" width="14.7734375" customWidth="true"/>
+    <col min="110" max="110" width="28.60546875" customWidth="true"/>
+    <col min="111" max="111" width="19.2109375" customWidth="true"/>
+    <col min="112" max="112" width="19.53515625" customWidth="true"/>
+    <col min="113" max="113" width="19.53515625" customWidth="true"/>
+    <col min="114" max="114" width="18.55859375" customWidth="true"/>
+    <col min="115" max="115" width="36.1015625" customWidth="true"/>
+    <col min="116" max="116" width="13.1328125" customWidth="true"/>
+    <col min="117" max="117" width="11.234375" customWidth="true"/>
+    <col min="118" max="118" width="14.14453125" customWidth="true"/>
+    <col min="119" max="119" width="18.82421875" customWidth="true"/>
+    <col min="120" max="120" width="19.76171875" customWidth="true"/>
+    <col min="121" max="121" width="19.7265625" customWidth="true"/>
+    <col min="122" max="122" width="13.50390625" customWidth="true"/>
+    <col min="123" max="123" width="29.76171875" customWidth="true"/>
+    <col min="124" max="124" width="11.234375" customWidth="true"/>
+    <col min="125" max="125" width="17.86328125" customWidth="true"/>
+    <col min="126" max="126" width="53.546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -200,535 +214,605 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>攻击力</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>生命值</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>基础护甲</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>防御升级奖励</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>攻击间隔</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>黄金消耗</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>木材消耗</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>图标 - 普通</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>模型文件</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>售出物品</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>需求 -使用等级数</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>训练单位</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>英雄技能</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>基础速度</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>占用人口</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>修理时间</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>路径纹理</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>目标允许</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>投射物图像</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>攻击类型</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>要求动画名</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>种族</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>热键 - 普通</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>魔法初始数量</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>魔法最大值</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>装甲类型</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>缩放</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>隐藏小地图显示</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
         <is>
           <t>主属性</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>初始力量</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>初始敏捷</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>初始智力</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>每等级提升力量</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>每等级提升敏捷</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>每等级提升智力</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>颜色值(红)</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>颜色值(绿)</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>颜色值(蓝)</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>高度</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>提示工具 -唤醒</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>视野范围(白天)</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>视野范围(夜晚)</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>模型缩放</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>按钮位置 - 普通 (X)</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>按钮位置 - 普通 (Y)</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>最大库存量</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>建筑地面纹理</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>修理金子消耗</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>购买时间间隔</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>建筑升级</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>武器类型</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>可建造建筑</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>建造时间</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>售出单位</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>购买开始时间</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>阴影图像(单位)</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
         <is>
           <t>编辑器后缀</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>动画伤害点</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>阴影图像(建筑)</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>攻击 2 - 投射物图像</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>攻击武器声音</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>射弹弧度</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>射弹速率</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>攻击 2 - 射弹速率</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
         <is>
           <t>攻击 2 - 攻击类型</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>生命回复类型</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>动画回复点</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>护甲类型</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>伤害骰子数量</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>动画 - 转向角度</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
         <is>
           <t>最小高度</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>转身速度</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>使用科技</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>阴影图像 - 高度</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>阴影图像 - X轴偏移</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>阴影图像 - Y轴偏移</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>魔法回复</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>阴影图像 - 宽度</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
         <is>
           <t>默认主动技能</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>黄金奖励 - 骰子数量</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>高度变化 - 采样范围</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>动画 - 混合时间(秒)</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
         <is>
           <t>穿透伤害距离</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>攻击范围</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>攻击 2 - 攻击范围</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>图标 - 计分屏</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>动画 - 行走速度</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>允许攻击模式</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>称谓</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>射弹自导允许</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>深水区有阴影</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
         <is>
           <t>主动攻击范围</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>死亡类型</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>动画 - 跑步速度</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>黄金奖励 - 骰子面数</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>提示工具 -重生</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>称谓数量</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>生命回复</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>单位声音设置</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>需求 - 等级 3</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>需求 - 等级 2</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>修理木材消耗</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>要求动画名 - 附加动画</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>伤害骰子面数</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>攻击间隔2</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>碰撞体积</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>黄金奖励 - 基础值</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>动画 - 魔法施放回复</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>穿透伤害范围</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>死亡时间(秒)</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
         <is>
           <t>木材奖励 - 基础值</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>是一个建筑</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>动画 - 魔法施放点</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>编辑器附加数据</t>
         </is>
@@ -762,535 +846,605 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>dmgplus1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>def</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>defUp</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>cool1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>goldcost</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>lumbercost</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Art</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Sellitems</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Requires</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Requirescount</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Trains</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>abilList</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>heroAbilList</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>spd</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>fused</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>reptm</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>pathTex</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>targs1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Missileart_1</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>atkType1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>animProps</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hotkey</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>mana0</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>manaN</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>movetp</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>armor</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>scale</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>hideOnMinimap</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>STRplus</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>AGIplus</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>INTplus</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>moveHeight</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>Awakentip</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>sight</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>nsight</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>modelScale</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>Buttonpos_1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>Buttonpos_2</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>stockMax</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>uberSplat</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>goldRep</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>stockRegen</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>Upgrade</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>weapTp1</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>Builds</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>bldtm</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>Sellunits</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>stockStart</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>unitShadow</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>EditorSuffix</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>dmgpt1</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>buildingShadow</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>Missileart_2</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>weapType1</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>Missilearc_1</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>Missilespeed_1</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>Missilespeed_2</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>Specialart</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
         <is>
           <t>atkType2</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>regenType</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>backSw1</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>defType</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>dice1</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>propWin</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
         <is>
           <t>moveFloor</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>turnRate</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>upgrades</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>shadowH</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>shadowX</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>shadowY</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>regenMana</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>shadowW</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>bountydice</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>elevRad</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>blend</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
         <is>
           <t>spillDist1</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>rangeN1</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>rangeN2</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>ScoreScreenIcon</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>weapsOn</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>Propernames</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>MissileHoming_1</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>shadowOnWater</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
         <is>
           <t>acquire</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>deathType</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>bountysides</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>Revivetip</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>nameCount</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>regenHP</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>unitSound</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>Requires2</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>Requires1</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>lumberRep</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Attachmentanimprops</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>sides1</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>cool2</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>collision</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>bountyplus</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>castbsw</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>spillRadius1</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
         <is>
           <t>lumberbountyplus</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>isbldg</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>castpt</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>W2LObject</t>
         </is>
@@ -1312,81 +1466,97 @@
           <t>召唤丛林守护者(|cffffcc00K|r)</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>TALT</t>
         </is>
       </c>
-      <c r="Q3" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Ault,AInv</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="AF3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="BA3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3600.0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>Rema</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
+      <c r="DH3" t="inlineStr">
         <is>
           <t>TWN3,TALT</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="DI3" t="inlineStr">
         <is>
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="DE3" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="DH3" t="inlineStr">
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1403,72 +1573,82 @@
           <t>Emoo</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Adtg,AInv,Ault</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="BP4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="BQ4" t="n">
-        <v>1100.0</v>
-      </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
         <is>
           <t>Reib</t>
         </is>
       </c>
-      <c r="CE4" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="DH4" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="DI4" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CZ4" t="inlineStr">
+      <c r="DM4" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="DH4" t="inlineStr">
+      <c r="DV4" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1485,53 +1665,57 @@
           <t>Ewar</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>A0DB,AInv,Ault</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="X5" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
         <is>
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="DE5" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="DH5" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="DI5" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="DA5" t="inlineStr">
+      <c r="DN5" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="DH5" t="inlineStr">
+      <c r="DV5" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1548,61 +1732,67 @@
           <t>Ewrd</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>A044,AInv,Ault</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>（玛维）</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>Remg,Rema,Reuv</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="DE6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="DH6" t="inlineStr">
+      <c r="DV6" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1634,204 +1824,232 @@
           <t>一名优秀的战士，但由于偷学禁招“水月斩”被封印起来，解救她，她就会为您效力。解救她需要500点蓝。</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>400.0</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>ReplaceableTextures\CommandButtons\BTNSeaWitch.blp</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Units\Naga\NagaSummoner\NagaSummoner.mdl</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>A09V,AInv</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>ground,ward,structure,debris,item</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>.mdl</t>
         </is>
       </c>
-      <c r="AE7" t="n">
-        <v>700.0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AM7" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="BA7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1500.0</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>Abilities\Weapons\WaterElementalMissile\WaterElementalMissile.mdl</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>MetalHeavySlice</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
         <is>
           <t>spells</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>Rnam,Rnat,Rguv</t>
         </is>
       </c>
-      <c r="CE7" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNSeaWitch.blp</t>
         </is>
       </c>
-      <c r="CI7" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
         <is>
           <t>索菲</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>800.0</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="DC7" t="inlineStr">
         <is>
           <t>复活娜迦海妖(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="DE7" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="DF7" t="inlineStr">
         <is>
           <t>NagaSiren</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
+      <c r="DH7" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="DI7" t="inlineStr">
         <is>
           <t>nnsa,nnad</t>
         </is>
       </c>
-      <c r="CW7" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="CZ7" t="inlineStr">
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="DA7" t="inlineStr">
+      <c r="DN7" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="DH7" t="inlineStr">
+      <c r="DV7" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1853,78 +2071,92 @@
           <t>黑暗骑士</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>350.0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AG8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>horse</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="AW8" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="CJ8" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
           <t>黑暗骑士</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="DC8" t="inlineStr">
         <is>
           <t>复活黑暗骑士(|cffffcc00L|r)</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CY8" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="DH8" t="inlineStr">
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -1956,240 +2188,282 @@
           <t>支援型英雄，非常擅长强劲的火力输出，有着高超的射击技巧，但很依赖装备</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNMarine.blp</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Units\Critters\Marine\Marine.mdl</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>TALT</t>
         </is>
       </c>
-      <c r="Q9" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>A09X,A09P</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>ground,ward,structure,tree,debris,item,air</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Abilities\Weapons\Rifle\RifleImpact.mdl</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AE9" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AL9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>155.0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>155.0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>55.0</v>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AW9" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="AY9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
         <is>
           <t>mline</t>
         </is>
       </c>
-      <c r="BJ9" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.17</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BQ9" t="n">
-        <v>10000.0</v>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BW9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>Rguv</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
         <is>
           <t>A0AM</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="CE9" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNMarine.blp</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>掉队士兵</t>
         </is>
       </c>
-      <c r="CK9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="DC9" t="inlineStr">
         <is>
           <t>复活机枪兵(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="DF9" t="inlineStr">
         <is>
           <t>Uther</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
+      <c r="DG9" t="inlineStr">
         <is>
           <t>mechanical</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
+      <c r="DH9" t="inlineStr">
         <is>
           <t>TWN3,TALT</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="DI9" t="inlineStr">
         <is>
           <t>TWN2,TALT</t>
         </is>
       </c>
-      <c r="CY9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="DD9" t="inlineStr">
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="DH9" t="inlineStr">
+      <c r="DV9" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2221,103 +2495,117 @@
           <t>半神宙斯……</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>300.0</v>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNAvatar.blp</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Apg2,AInv</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AC10" t="inlineStr">
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>alternate</t>
         </is>
       </c>
-      <c r="AF10" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>24.0</v>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>复活宙斯(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNAvatar.blp</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>宙斯</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="DC10" t="inlineStr">
         <is>
           <t>复活宙斯(|cffffcc00M|r)</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="DF10" t="inlineStr">
         <is>
           <t>Muradin</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
+      <c r="DH10" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="DI10" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="DH10" t="inlineStr">
+      <c r="DV10" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2339,52 +2627,62 @@
           <t>战士型英雄，特别擅长于冲锋陷阵。最终技能：狂暴矮人</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>300.0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
         <is>
           <t>Rhan,Rhla</t>
         </is>
       </c>
-      <c r="CU11" t="inlineStr">
+      <c r="DH11" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="DI11" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="DH11" t="inlineStr">
+      <c r="DV11" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2406,96 +2704,122 @@
           <t>娜迦女海巫(|cffffcc00N|r)</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>A01B,A09V,AInv</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AB12" t="inlineStr">
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>pierce</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1500.0</v>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BQ12" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
         <is>
           <t>Rguv,R001</t>
         </is>
       </c>
-      <c r="CE12" t="n">
-        <v>900.0</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CU12" t="inlineStr">
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="DE12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DH12" t="inlineStr">
         <is>
           <t>TWN3</t>
         </is>
       </c>
-      <c r="CV12" t="inlineStr">
+      <c r="DI12" t="inlineStr">
         <is>
           <t>TWN2</t>
         </is>
       </c>
-      <c r="CW12" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="DA12" t="inlineStr">
+      <c r="DJ12" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="DN12" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="DH12" t="inlineStr">
+      <c r="DV12" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2527,178 +2851,202 @@
           <t>服部半藏</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>200.0</v>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>ReplaceableTextures\CommandButtons\BTNChaosBlademaster.blp</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>units\demon\HeroChaosBladeMaster\HeroChaosBladeMaster.mdl</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>AInv,A0PD</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
-      <c r="AF13" t="n">
-        <v>90.0</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
           <t>Flesh</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AK13" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>16.0</v>
-      </c>
       <c r="AN13" t="inlineStr">
         <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AR13" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="AU13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="BJ13" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
         <is>
           <t>(剑魔附身)</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BY13" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="BW13" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="BZ13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
         <is>
           <t>Robs,Roar</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CS13" t="inlineStr">
         <is>
           <t>UI\Glues\ScoreScreen\scorescreen-hero-chaosblademaster.blp</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CT13" t="inlineStr">
         <is>
           <t>290.0</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CV13" t="inlineStr">
         <is>
           <t>服部半藏</t>
         </is>
       </c>
-      <c r="CN13" t="inlineStr">
+      <c r="DA13" t="inlineStr">
         <is>
           <t>300.0</t>
         </is>
       </c>
-      <c r="CP13" t="inlineStr">
+      <c r="DC13" t="inlineStr">
         <is>
           <t>(|cffffcc00X|r)复活服部半藏</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CR13" t="inlineStr">
+      <c r="DD13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DE13" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="CS13" t="inlineStr">
+      <c r="DF13" t="inlineStr">
         <is>
           <t>HeroBladeMaster</t>
         </is>
       </c>
-      <c r="CT13" t="inlineStr">
+      <c r="DG13" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="CX13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CY13" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="DG13" t="inlineStr">
+      <c r="DK13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL13" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="DU13" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="DH13" t="inlineStr">
+      <c r="DV13" t="inlineStr">
         <is>
           <t>"XC":"英雄.xlsx  【英雄技能.uobj】  "</t>
         </is>
@@ -2730,22 +3078,19 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2753,159 +3098,192 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V14" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z14" t="inlineStr">
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="AE14" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AG14" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AK14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.0</v>
-      </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV14" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="BL14" t="inlineStr">
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BQ14" t="n">
-        <v>950.0</v>
-      </c>
       <c r="BU14" t="inlineStr">
         <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY14" t="inlineStr">
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE14" t="n">
-        <v>1000.0</v>
-      </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CL14" t="inlineStr">
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ14" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CP14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CQ14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CR14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CU14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="CV14" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY14" t="n">
-        <v>1.0</v>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="DC14" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DG14" t="inlineStr">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DD14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DE14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DF14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DP14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DU14" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -2937,17 +3315,14 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2955,151 +3330,182 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V15" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z15" t="inlineStr">
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="AE15" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="AK15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.0</v>
-      </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV15" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="BL15" t="inlineStr">
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BQ15" t="n">
-        <v>950.0</v>
-      </c>
       <c r="BU15" t="inlineStr">
         <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY15" t="inlineStr">
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE15" t="n">
-        <v>1000.0</v>
-      </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CL15" t="inlineStr">
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ15" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CP15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CQ15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CU15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="CV15" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY15" t="n">
-        <v>1.0</v>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="DC15" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DG15" t="inlineStr">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DD15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DE15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DF15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DP15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DU15" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3131,22 +3537,19 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -3154,164 +3557,197 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V16" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="AE16" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="AK16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.0</v>
-      </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV16" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="BL16" t="inlineStr">
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BQ16" t="n">
-        <v>950.0</v>
-      </c>
       <c r="BU16" t="inlineStr">
         <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY16" t="inlineStr">
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE16" t="n">
-        <v>1000.0</v>
-      </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CL16" t="inlineStr">
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ16" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CP16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CQ16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CR16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CU16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="CV16" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY16" t="n">
-        <v>1.0</v>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="DC16" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DG16" t="inlineStr">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DD16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DE16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DF16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DH16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DP16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DU16" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3343,17 +3779,14 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -3361,146 +3794,177 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V17" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z17" t="inlineStr">
+      <c r="U17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="AE17" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AG17" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AK17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.0</v>
-      </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV17" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="BL17" t="inlineStr">
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BQ17" t="n">
-        <v>950.0</v>
-      </c>
       <c r="BU17" t="inlineStr">
         <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY17" t="inlineStr">
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="CA17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE17" t="n">
-        <v>1000.0</v>
-      </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CL17" t="inlineStr">
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ17" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CP17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CQ17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CU17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="CV17" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY17" t="n">
-        <v>1.0</v>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="DC17" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DG17" t="inlineStr">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DD17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DE17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DF17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DH17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DP17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DU17" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3532,22 +3996,19 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -3555,164 +4016,197 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V18" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z18" t="inlineStr">
+      <c r="U18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="AE18" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AG18" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="AK18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.0</v>
-      </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV18" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="BL18" t="inlineStr">
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BQ18" t="n">
-        <v>950.0</v>
-      </c>
       <c r="BU18" t="inlineStr">
         <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY18" t="inlineStr">
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="CA18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE18" t="n">
-        <v>1000.0</v>
-      </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CK18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CL18" t="inlineStr">
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ18" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CP18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CQ18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CU18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="CV18" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY18" t="n">
-        <v>1.0</v>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="DC18" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DG18" t="inlineStr">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DD18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DE18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DF18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DH18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DP18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DU18" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3744,17 +4238,14 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3762,151 +4253,182 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="V19" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z19" t="inlineStr">
+      <c r="U19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Objects\Spawnmodels\Critters\Albatross\CritterBloodAlbatross.mdl</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AG19" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AM19" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="AK19" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.0</v>
-      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV19" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3000.0</v>
-      </c>
-      <c r="BL19" t="inlineStr">
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BQ19" t="n">
-        <v>950.0</v>
-      </c>
       <c r="BU19" t="inlineStr">
         <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BW19" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY19" t="inlineStr">
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE19" t="n">
-        <v>1000.0</v>
-      </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CL19" t="inlineStr">
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ19" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CP19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CQ19" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CU19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="CV19" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="CY19" t="n">
-        <v>1.0</v>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="DC19" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DG19" t="inlineStr">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DD19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DE19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DF19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DH19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DP19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DU19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3933,42 +4455,42 @@
           <t>地精商店模板</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>units\human\Jaina\Jaina.mdl</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Ecen</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Ecen</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Aneu,Avul,Apit</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
         <is>
           <t>Ecen</t>
         </is>
       </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="DH20" t="inlineStr">
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DV20" t="inlineStr">
         <is>
           <t>"XC":"商店NPC.xlsx  【商店npc.uobj】  "</t>
         </is>
@@ -4000,126 +4522,162 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AV21" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BL21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BQ21" t="n">
-        <v>900.0</v>
-      </c>
       <c r="BU21" t="inlineStr">
         <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BV21" t="inlineStr">
+      <c r="CA21" t="inlineStr">
         <is>
           <t>hero</t>
         </is>
       </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CC21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE21" t="n">
-        <v>128.0</v>
-      </c>
-      <c r="CL21" t="inlineStr">
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CM21" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CO21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CR21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CY21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DB21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DC21" t="inlineStr">
+      <c r="CZ21" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="DB21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DE21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DL21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DO21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP21" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG21" t="inlineStr">
+      <c r="DU21" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4151,113 +4709,147 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>ground,structure,air,item,ward</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AV22" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BL22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
+      <c r="BZ22" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BV22" t="inlineStr">
+      <c r="CA22" t="inlineStr">
         <is>
           <t>hero</t>
         </is>
       </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CC22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE22" t="n">
-        <v>128.0</v>
-      </c>
-      <c r="CL22" t="inlineStr">
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CM22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
         <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="CM22" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CO22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CR22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CY22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DB22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DC22" t="inlineStr">
+      <c r="CZ22" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="DB22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DE22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DL22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DO22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP22" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG22" t="inlineStr">
+      <c r="DU22" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4289,59 +4881,77 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>units\human\Jaina\Jaina.mdx</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Aneu,Asid,Avul,Asud,Apit</t>
         </is>
       </c>
-      <c r="V23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV23" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="BZ23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CI23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DC23" t="inlineStr">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CU23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP23" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DF23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="DG23" t="inlineStr">
+      <c r="DT23" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DU23" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4373,53 +4983,67 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>units\human\Jaina\Jaina.mdx</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Aneu,Asid,Avul,Asud,Apit</t>
         </is>
       </c>
-      <c r="V24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG24" t="inlineStr">
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
         <is>
           <t>fly</t>
         </is>
       </c>
-      <c r="AV24" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BZ24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CI24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DC24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CU24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP24" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DF24" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="DG24" t="inlineStr">
+      <c r="DT24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DU24" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4446,106 +5070,122 @@
           <t>宝宝助手</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>ReplaceableTextures\CommandButtons\BTNSnowOwl.blp</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>units\critters\SnowOwl\SnowOwl.mdx</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Avul,AInv</t>
         </is>
       </c>
-      <c r="V25" t="n">
-        <v>522.0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000.0</v>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>522.0</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
           <t>fly</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AW25" t="inlineStr">
         <is>
           <t>240.0</t>
         </is>
       </c>
-      <c r="AV25" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BX25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="BY25" t="inlineStr">
+      <c r="CE25" t="inlineStr">
         <is>
           <t>2.99</t>
         </is>
       </c>
-      <c r="BZ25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CA25" t="inlineStr">
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="CI25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CL25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="DA25" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="DC25" t="inlineStr">
+      <c r="CU25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DN25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="DP25" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG25" t="inlineStr">
+      <c r="DU25" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4577,59 +5217,77 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="X26" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV26" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="BZ26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CW26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DC26" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DJ26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP26" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG26" t="inlineStr">
+      <c r="DU26" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4661,51 +5319,67 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="X27" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BE27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BH27" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="BZ27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CW27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DC27" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DJ27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP27" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG27" t="inlineStr">
+      <c r="DU27" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4737,66 +5411,82 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="X28" t="n">
-        <v>3.0</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AV28" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BC28" t="n">
-        <v>0.0</v>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="BH28" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="BM28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="BZ28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CW28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DC28" t="inlineStr">
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CF28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DJ28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP28" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG28" t="inlineStr">
+      <c r="DU28" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4823,62 +5513,72 @@
           <t>金矿</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>Agld</t>
         </is>
       </c>
-      <c r="X29" t="n">
-        <v>3.0</v>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>PathTextures\4x4SimpleSolid.tga</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AK29" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="AV29" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BB29" t="inlineStr">
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
         <is>
           <t>HSMA</t>
         </is>
       </c>
-      <c r="BH29" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="BM29" t="inlineStr">
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BQ29" t="inlineStr">
         <is>
           <t>BuildingShadowSmall</t>
         </is>
       </c>
-      <c r="BZ29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="CT29" t="inlineStr">
+      <c r="CF29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DG29" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
       </c>
-      <c r="DC29" t="inlineStr">
+      <c r="DP29" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG29" t="inlineStr">
+      <c r="DU29" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -4910,41 +5610,281 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="W30" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG30" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
         <is>
           <t>amph</t>
         </is>
       </c>
-      <c r="AV30" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="BZ30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="DC30" t="inlineStr">
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="CF30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DP30" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="DG30" t="inlineStr">
+      <c r="DU30" t="inlineStr">
         <is>
           <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>h000</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>hpea</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>马甲</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>|cffBA55D3我</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>|cffBA55D3我</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>|cffBA55D3我</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>.mdx</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Aloc</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BN31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BP31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BW31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BZ31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CC31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CE31" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="CF31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="CG31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CI31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CJ31" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="CK31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CN31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CO31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CT31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CU31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CX31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DA31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DE31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="DF31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DG31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="DL31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DN31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DP31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DR31" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="DU31" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
